--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.13ログ.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.13ログ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\gitbucket\Fintan\application-architecture-sample\nablarch_sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\t-uchida\projects\github.com\Fintan-contents\application-architecture-sample\nablarch_sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4157B466-4D97-4793-9BC8-D97C3572D049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FB4906-BC06-47F9-AC8E-5550FF0DA748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.13.ログ" sheetId="2" r:id="rId1"/>
@@ -1129,22 +1129,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/log/failure_log.html#failure-log-setting</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/log/sql_log.html#sql-log-setting</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/log/http_access_log.html#http-access-log-setting</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://nablarch.github.io/docs/LATEST/doc/application_framework/application_framework/libraries/log/performance_log.html#performance-log-setting</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>※実行状況ログについては、フォーマットの指定はできないためNablarchが出力するものをそのまま使用する。</t>
     <rPh sb="20" eb="22">
       <t>シテイ</t>
@@ -1509,6 +1493,22 @@
     <rPh sb="52" eb="54">
       <t>シヨウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/log/failure_log.html#failure-log-setting</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/log/http_access_log.html#http-access-log-setting</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/log/sql_log.html#sql-log-setting</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/log/performance_log.html#performance-log-setting</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1582,7 +1582,7 @@
       <sz val="9"/>
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -2353,13 +2353,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AS244"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="3.625" style="45"/>
-    <col min="3" max="16384" width="3.625" style="4"/>
+    <col min="1" max="2" width="3.6328125" style="45"/>
+    <col min="3" max="16384" width="3.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>140</v>
       </c>
@@ -2404,7 +2404,7 @@
       <c r="AH1" s="75"/>
       <c r="AI1" s="76"/>
     </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -2449,7 +2449,7 @@
       <c r="AH2" s="75"/>
       <c r="AI2" s="76"/>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2490,8 +2490,8 @@
       <c r="AH3" s="75"/>
       <c r="AI3" s="76"/>
     </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="46" t="s">
         <v>155</v>
       </c>
@@ -2499,8 +2499,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="46" t="str">
         <f>$B$5&amp;"13."</f>
         <v>7.13.</v>
@@ -2509,17 +2509,17 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="46"/>
       <c r="D8" s="45" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AF9" s="45"/>
       <c r="AG9" s="45"/>
     </row>
-    <row r="10" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45"/>
       <c r="B10" s="45"/>
       <c r="D10" s="17" t="str">
@@ -2532,7 +2532,7 @@
       <c r="AF10" s="45"/>
       <c r="AG10" s="45"/>
     </row>
-    <row r="11" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="45"/>
       <c r="B11" s="45"/>
       <c r="D11" s="17"/>
@@ -2546,7 +2546,7 @@
       <c r="AF11" s="45"/>
       <c r="AG11" s="45"/>
     </row>
-    <row r="12" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45"/>
       <c r="B12" s="45"/>
       <c r="D12" s="17"/>
@@ -2557,7 +2557,7 @@
       <c r="AF12" s="45"/>
       <c r="AG12" s="45"/>
     </row>
-    <row r="13" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45"/>
       <c r="B13" s="45"/>
       <c r="D13" s="17"/>
@@ -2599,7 +2599,7 @@
       <c r="AH13" s="55"/>
       <c r="AI13" s="56"/>
     </row>
-    <row r="14" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="46"/>
       <c r="E14" s="46"/>
       <c r="F14" s="51"/>
@@ -2635,7 +2635,7 @@
       <c r="AH14" s="52"/>
       <c r="AI14" s="53"/>
     </row>
-    <row r="15" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="45"/>
       <c r="B15" s="45"/>
       <c r="D15" s="17"/>
@@ -2677,7 +2677,7 @@
       <c r="AH15" s="24"/>
       <c r="AI15" s="25"/>
     </row>
-    <row r="16" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="46"/>
       <c r="E16" s="46"/>
       <c r="F16" s="35"/>
@@ -2713,7 +2713,7 @@
       <c r="AH16" s="41"/>
       <c r="AI16" s="42"/>
     </row>
-    <row r="17" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="45"/>
       <c r="B17" s="45"/>
       <c r="D17" s="17"/>
@@ -2755,7 +2755,7 @@
       <c r="AH17" s="19"/>
       <c r="AI17" s="20"/>
     </row>
-    <row r="18" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45"/>
       <c r="B18" s="45"/>
       <c r="D18" s="17"/>
@@ -2793,7 +2793,7 @@
       <c r="AH18" s="22"/>
       <c r="AI18" s="26"/>
     </row>
-    <row r="19" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="45"/>
       <c r="B19" s="45"/>
       <c r="D19" s="17"/>
@@ -2836,7 +2836,7 @@
       <c r="AI19" s="20"/>
       <c r="AK19" s="45"/>
     </row>
-    <row r="20" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45"/>
       <c r="B20" s="45"/>
       <c r="D20" s="17"/>
@@ -2875,7 +2875,7 @@
       <c r="AI20" s="20"/>
       <c r="AK20" s="45"/>
     </row>
-    <row r="21" spans="1:37" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:37" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D21" s="46"/>
       <c r="E21" s="46"/>
       <c r="F21" s="40"/>
@@ -2911,7 +2911,7 @@
       <c r="AH21" s="41"/>
       <c r="AI21" s="42"/>
     </row>
-    <row r="22" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45"/>
       <c r="B22" s="45"/>
       <c r="D22" s="17"/>
@@ -2953,7 +2953,7 @@
       <c r="AH22" s="19"/>
       <c r="AI22" s="20"/>
     </row>
-    <row r="23" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="D23" s="17"/>
@@ -2989,7 +2989,7 @@
       <c r="AH23" s="22"/>
       <c r="AI23" s="26"/>
     </row>
-    <row r="24" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="45"/>
       <c r="B24" s="45"/>
       <c r="D24" s="17"/>
@@ -3031,7 +3031,7 @@
       <c r="AH24" s="19"/>
       <c r="AI24" s="20"/>
     </row>
-    <row r="25" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="45"/>
       <c r="B25" s="45"/>
       <c r="D25" s="17"/>
@@ -3067,7 +3067,7 @@
       <c r="AH25" s="22"/>
       <c r="AI25" s="26"/>
     </row>
-    <row r="26" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="45"/>
       <c r="B26" s="45"/>
       <c r="D26" s="17"/>
@@ -3109,7 +3109,7 @@
       <c r="AH26" s="19"/>
       <c r="AI26" s="20"/>
     </row>
-    <row r="27" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="45"/>
       <c r="B27" s="45"/>
       <c r="D27" s="17"/>
@@ -3145,7 +3145,7 @@
       <c r="AH27" s="22"/>
       <c r="AI27" s="26"/>
     </row>
-    <row r="28" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="45"/>
       <c r="B28" s="45"/>
       <c r="D28" s="17"/>
@@ -3153,7 +3153,7 @@
       <c r="AE28" s="45"/>
       <c r="AF28" s="45"/>
     </row>
-    <row r="29" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="45"/>
       <c r="B29" s="45"/>
       <c r="D29" s="17"/>
@@ -3164,7 +3164,7 @@
       <c r="AE29" s="45"/>
       <c r="AF29" s="45"/>
     </row>
-    <row r="30" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="45"/>
       <c r="B30" s="45"/>
       <c r="D30" s="17"/>
@@ -3206,7 +3206,7 @@
       <c r="AH30" s="28"/>
       <c r="AI30" s="29"/>
     </row>
-    <row r="31" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="45"/>
       <c r="B31" s="45"/>
       <c r="D31" s="38"/>
@@ -3249,7 +3249,7 @@
       <c r="AH31" s="43"/>
       <c r="AI31" s="44"/>
     </row>
-    <row r="32" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="45"/>
       <c r="B32" s="45"/>
       <c r="D32" s="17"/>
@@ -3292,7 +3292,7 @@
       <c r="AH32" s="43"/>
       <c r="AI32" s="44"/>
     </row>
-    <row r="33" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="45"/>
       <c r="B33" s="45"/>
       <c r="D33" s="17"/>
@@ -3335,7 +3335,7 @@
       <c r="AH33" s="43"/>
       <c r="AI33" s="44"/>
     </row>
-    <row r="34" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="45"/>
       <c r="B34" s="45"/>
       <c r="D34" s="17"/>
@@ -3378,7 +3378,7 @@
       <c r="AH34" s="43"/>
       <c r="AI34" s="44"/>
     </row>
-    <row r="35" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="45"/>
       <c r="B35" s="45"/>
       <c r="D35" s="17"/>
@@ -3421,7 +3421,7 @@
       <c r="AH35" s="24"/>
       <c r="AI35" s="25"/>
     </row>
-    <row r="36" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D36" s="46"/>
       <c r="E36" s="46"/>
       <c r="F36" s="40"/>
@@ -3459,7 +3459,7 @@
       <c r="AH36" s="41"/>
       <c r="AI36" s="42"/>
     </row>
-    <row r="37" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="45"/>
       <c r="B37" s="45"/>
       <c r="D37" s="17"/>
@@ -3502,7 +3502,7 @@
       <c r="AH37" s="24"/>
       <c r="AI37" s="25"/>
     </row>
-    <row r="38" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D38" s="46"/>
       <c r="E38" s="46"/>
       <c r="F38" s="40"/>
@@ -3554,7 +3554,7 @@
       <c r="AF40" s="45"/>
       <c r="AG40" s="45"/>
     </row>
-    <row r="41" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="45"/>
       <c r="B41" s="45"/>
       <c r="D41" s="17"/>
@@ -3568,7 +3568,7 @@
       <c r="AF41" s="45"/>
       <c r="AG41" s="45"/>
     </row>
-    <row r="42" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="45"/>
       <c r="B42" s="45"/>
       <c r="D42" s="17"/>
@@ -3579,7 +3579,7 @@
       <c r="AF42" s="45"/>
       <c r="AG42" s="45"/>
     </row>
-    <row r="43" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="45"/>
       <c r="B43" s="45"/>
       <c r="F43" s="27" t="s">
@@ -3619,7 +3619,7 @@
       <c r="AH43" s="28"/>
       <c r="AI43" s="29"/>
     </row>
-    <row r="44" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="45"/>
       <c r="B44" s="45"/>
       <c r="F44" s="32" t="s">
@@ -3659,7 +3659,7 @@
       <c r="AH44" s="33"/>
       <c r="AI44" s="34"/>
     </row>
-    <row r="45" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="45"/>
       <c r="B45" s="45"/>
       <c r="F45" s="18" t="s">
@@ -3699,7 +3699,7 @@
       <c r="AH45" s="19"/>
       <c r="AI45" s="20"/>
     </row>
-    <row r="46" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F46" s="18"/>
       <c r="G46" s="19"/>
       <c r="H46" s="19"/>
@@ -3733,7 +3733,7 @@
       <c r="AH46" s="19"/>
       <c r="AI46" s="20"/>
     </row>
-    <row r="47" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="45"/>
       <c r="B47" s="45"/>
       <c r="F47" s="21"/>
@@ -3769,7 +3769,7 @@
       <c r="AH47" s="22"/>
       <c r="AI47" s="26"/>
     </row>
-    <row r="48" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="45"/>
       <c r="B48" s="45"/>
       <c r="F48" s="18" t="s">
@@ -3809,7 +3809,7 @@
       <c r="AH48" s="19"/>
       <c r="AI48" s="20"/>
     </row>
-    <row r="49" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F49" s="18"/>
       <c r="G49" s="19"/>
       <c r="H49" s="19"/>
@@ -3843,7 +3843,7 @@
       <c r="AH49" s="19"/>
       <c r="AI49" s="20"/>
     </row>
-    <row r="50" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="45"/>
       <c r="B50" s="45"/>
       <c r="F50" s="21"/>
@@ -3879,7 +3879,7 @@
       <c r="AH50" s="22"/>
       <c r="AI50" s="26"/>
     </row>
-    <row r="51" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="45"/>
       <c r="B51" s="45"/>
       <c r="F51" s="18" t="s">
@@ -3919,7 +3919,7 @@
       <c r="AH51" s="19"/>
       <c r="AI51" s="20"/>
     </row>
-    <row r="52" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="45"/>
       <c r="B52" s="45"/>
       <c r="F52" s="21"/>
@@ -3955,7 +3955,7 @@
       <c r="AH52" s="22"/>
       <c r="AI52" s="26"/>
     </row>
-    <row r="53" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="45"/>
       <c r="B53" s="45"/>
       <c r="F53" s="18" t="s">
@@ -3995,7 +3995,7 @@
       <c r="AH53" s="19"/>
       <c r="AI53" s="20"/>
     </row>
-    <row r="54" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="45"/>
       <c r="B54" s="45"/>
       <c r="F54" s="18"/>
@@ -4031,7 +4031,7 @@
       <c r="AH54" s="19"/>
       <c r="AI54" s="20"/>
     </row>
-    <row r="55" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="45"/>
       <c r="B55" s="45"/>
       <c r="F55" s="18"/>
@@ -4067,7 +4067,7 @@
       <c r="AH55" s="19"/>
       <c r="AI55" s="20"/>
     </row>
-    <row r="56" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="45"/>
       <c r="B56" s="45"/>
       <c r="F56" s="18"/>
@@ -4103,7 +4103,7 @@
       <c r="AH56" s="19"/>
       <c r="AI56" s="20"/>
     </row>
-    <row r="57" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="45"/>
       <c r="B57" s="45"/>
       <c r="F57" s="18"/>
@@ -4139,7 +4139,7 @@
       <c r="AH57" s="19"/>
       <c r="AI57" s="20"/>
     </row>
-    <row r="58" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="45"/>
       <c r="B58" s="45"/>
       <c r="F58" s="18"/>
@@ -4175,7 +4175,7 @@
       <c r="AH58" s="19"/>
       <c r="AI58" s="20"/>
     </row>
-    <row r="59" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F59" s="18"/>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
@@ -4209,7 +4209,7 @@
       <c r="AH59" s="19"/>
       <c r="AI59" s="20"/>
     </row>
-    <row r="60" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="45"/>
       <c r="B60" s="45"/>
       <c r="F60" s="18"/>
@@ -4245,7 +4245,7 @@
       <c r="AH60" s="19"/>
       <c r="AI60" s="20"/>
     </row>
-    <row r="61" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="45"/>
       <c r="B61" s="45"/>
       <c r="F61" s="18"/>
@@ -4281,7 +4281,7 @@
       <c r="AH61" s="19"/>
       <c r="AI61" s="20"/>
     </row>
-    <row r="62" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="45"/>
       <c r="B62" s="45"/>
       <c r="F62" s="21"/>
@@ -4317,19 +4317,19 @@
       <c r="AH62" s="22"/>
       <c r="AI62" s="26"/>
     </row>
-    <row r="63" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="45"/>
       <c r="B63" s="45"/>
       <c r="AF63" s="45"/>
       <c r="AG63" s="45"/>
     </row>
-    <row r="64" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F64" s="45" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="45"/>
       <c r="B66" s="45"/>
       <c r="F66" s="19"/>
@@ -4364,7 +4364,7 @@
       <c r="AI66" s="19"/>
       <c r="AJ66" s="19"/>
     </row>
-    <row r="67" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="45"/>
       <c r="B67" s="45"/>
       <c r="E67" s="17" t="str">
@@ -4377,7 +4377,7 @@
       <c r="AF67" s="45"/>
       <c r="AG67" s="45"/>
     </row>
-    <row r="68" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="45"/>
       <c r="B68" s="45"/>
       <c r="F68" s="16" t="s">
@@ -4386,13 +4386,13 @@
       <c r="AF68" s="45"/>
       <c r="AG68" s="45"/>
     </row>
-    <row r="69" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="45"/>
       <c r="B69" s="45"/>
       <c r="AF69" s="45"/>
       <c r="AG69" s="45"/>
     </row>
-    <row r="70" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E70" s="46" t="str">
         <f>$D$10&amp;"4."</f>
         <v>7.13.1.4.</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G70" s="30"/>
     </row>
-    <row r="71" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="45"/>
       <c r="B71" s="45"/>
       <c r="E71" s="30"/>
@@ -4420,7 +4420,7 @@
       <c r="AF71" s="45"/>
       <c r="AG71" s="45"/>
     </row>
-    <row r="72" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="45"/>
       <c r="B72" s="45"/>
       <c r="E72" s="30"/>
@@ -4438,7 +4438,7 @@
       <c r="AF72" s="45"/>
       <c r="AG72" s="45"/>
     </row>
-    <row r="73" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="45"/>
       <c r="B73" s="45"/>
       <c r="E73" s="30"/>
@@ -4454,7 +4454,7 @@
       <c r="AF73" s="45"/>
       <c r="AG73" s="45"/>
     </row>
-    <row r="74" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="45"/>
       <c r="B74" s="45"/>
       <c r="E74" s="30"/>
@@ -4497,7 +4497,7 @@
       <c r="AR74" s="45"/>
       <c r="AS74" s="45"/>
     </row>
-    <row r="75" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="45"/>
       <c r="B75" s="45"/>
       <c r="E75" s="30"/>
@@ -4540,7 +4540,7 @@
       <c r="AR75" s="45"/>
       <c r="AS75" s="45"/>
     </row>
-    <row r="76" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E76" s="30"/>
       <c r="F76" s="40"/>
       <c r="G76" s="41"/>
@@ -4575,7 +4575,7 @@
       <c r="AH76" s="41"/>
       <c r="AI76" s="42"/>
     </row>
-    <row r="77" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="45"/>
       <c r="B77" s="45"/>
       <c r="E77" s="30"/>
@@ -4584,13 +4584,13 @@
       <c r="AF77" s="45"/>
       <c r="AG77" s="45"/>
     </row>
-    <row r="78" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="45"/>
       <c r="B78" s="45"/>
       <c r="AF78" s="45"/>
       <c r="AG78" s="45"/>
     </row>
-    <row r="79" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="45"/>
       <c r="B79" s="45"/>
       <c r="D79" s="46" t="str">
@@ -4603,7 +4603,7 @@
       <c r="AF79" s="45"/>
       <c r="AG79" s="45"/>
     </row>
-    <row r="80" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="45"/>
       <c r="B80" s="45"/>
       <c r="E80" s="17" t="str">
@@ -4616,7 +4616,7 @@
       <c r="AF80" s="45"/>
       <c r="AG80" s="45"/>
     </row>
-    <row r="81" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="45"/>
       <c r="B81" s="45"/>
       <c r="F81" s="17" t="s">
@@ -4628,17 +4628,17 @@
       <c r="AF81" s="45"/>
       <c r="AG81" s="45"/>
     </row>
-    <row r="82" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="45"/>
       <c r="B82" s="45"/>
       <c r="F82" s="17"/>
       <c r="G82" s="16" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AF82" s="45"/>
       <c r="AG82" s="45"/>
     </row>
-    <row r="83" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="45"/>
       <c r="B83" s="45"/>
       <c r="D83" s="15"/>
@@ -4677,7 +4677,7 @@
       <c r="AH83" s="28"/>
       <c r="AI83" s="29"/>
     </row>
-    <row r="84" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="45"/>
       <c r="B84" s="45"/>
       <c r="D84" s="15"/>
@@ -4716,7 +4716,7 @@
       <c r="AH84" s="43"/>
       <c r="AI84" s="44"/>
     </row>
-    <row r="85" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="45"/>
       <c r="B85" s="45"/>
       <c r="D85" s="15"/>
@@ -4755,23 +4755,23 @@
       <c r="AH85" s="43"/>
       <c r="AI85" s="44"/>
     </row>
-    <row r="86" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="45"/>
       <c r="B86" s="45"/>
       <c r="G86" s="17"/>
       <c r="AF86" s="45"/>
       <c r="AG86" s="45"/>
     </row>
-    <row r="87" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="45"/>
       <c r="B87" s="45"/>
       <c r="G87" s="16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AF87" s="45"/>
       <c r="AG87" s="45"/>
     </row>
-    <row r="88" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="45"/>
       <c r="B88" s="45"/>
       <c r="D88" s="15"/>
@@ -4805,20 +4805,20 @@
       <c r="Y88" s="28"/>
       <c r="Z88" s="29"/>
       <c r="AA88" s="27" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AB88" s="28"/>
       <c r="AC88" s="28"/>
       <c r="AD88" s="28"/>
       <c r="AE88" s="28"/>
       <c r="AF88" s="27" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AG88" s="28"/>
       <c r="AH88" s="28"/>
       <c r="AI88" s="29"/>
     </row>
-    <row r="89" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="45"/>
       <c r="B89" s="45"/>
       <c r="D89" s="15"/>
@@ -4832,7 +4832,7 @@
       <c r="J89" s="24"/>
       <c r="K89" s="24"/>
       <c r="L89" s="23" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M89" s="24"/>
       <c r="N89" s="24"/>
@@ -4866,7 +4866,7 @@
       <c r="AH89" s="24"/>
       <c r="AI89" s="25"/>
     </row>
-    <row r="90" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D90" s="15"/>
       <c r="E90" s="15"/>
       <c r="G90" s="23" t="str">
@@ -4884,7 +4884,7 @@
       <c r="N90" s="24"/>
       <c r="O90" s="24"/>
       <c r="P90" s="23" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="Q90" s="24"/>
       <c r="R90" s="24"/>
@@ -4906,13 +4906,13 @@
       <c r="AD90" s="24"/>
       <c r="AE90" s="24"/>
       <c r="AF90" s="23" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AG90" s="24"/>
       <c r="AH90" s="24"/>
       <c r="AI90" s="25"/>
     </row>
-    <row r="91" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="45"/>
       <c r="B91" s="45"/>
       <c r="D91" s="15"/>
@@ -4926,7 +4926,7 @@
       <c r="J91" s="24"/>
       <c r="K91" s="24"/>
       <c r="L91" s="23" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M91" s="24"/>
       <c r="N91" s="24"/>
@@ -4960,7 +4960,7 @@
       <c r="AH91" s="24"/>
       <c r="AI91" s="25"/>
     </row>
-    <row r="92" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="45"/>
       <c r="B92" s="45"/>
       <c r="D92" s="15"/>
@@ -4997,7 +4997,7 @@
       <c r="AH92" s="19"/>
       <c r="AI92" s="20"/>
     </row>
-    <row r="93" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="45"/>
       <c r="B93" s="45"/>
       <c r="D93" s="15"/>
@@ -5034,7 +5034,7 @@
       <c r="AH93" s="19"/>
       <c r="AI93" s="20"/>
     </row>
-    <row r="94" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D94" s="15"/>
       <c r="E94" s="15"/>
       <c r="G94" s="40"/>
@@ -5069,7 +5069,7 @@
       <c r="AH94" s="41"/>
       <c r="AI94" s="42"/>
     </row>
-    <row r="95" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D95" s="15"/>
       <c r="E95" s="15"/>
       <c r="G95" s="23" t="str">
@@ -5087,7 +5087,7 @@
       <c r="N95" s="24"/>
       <c r="O95" s="24"/>
       <c r="P95" s="23" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Q95" s="24"/>
       <c r="R95" s="24"/>
@@ -5109,13 +5109,13 @@
       <c r="AD95" s="24"/>
       <c r="AE95" s="25"/>
       <c r="AF95" s="23" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AG95" s="24"/>
       <c r="AH95" s="24"/>
       <c r="AI95" s="25"/>
     </row>
-    <row r="96" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D96" s="15"/>
       <c r="E96" s="15"/>
       <c r="G96" s="18"/>
@@ -5150,7 +5150,7 @@
       <c r="AH96" s="19"/>
       <c r="AI96" s="20"/>
     </row>
-    <row r="97" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D97" s="15"/>
       <c r="E97" s="15"/>
       <c r="G97" s="40"/>
@@ -5185,7 +5185,7 @@
       <c r="AH97" s="41"/>
       <c r="AI97" s="42"/>
     </row>
-    <row r="98" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="45"/>
       <c r="B98" s="45"/>
       <c r="D98" s="15"/>
@@ -5220,7 +5220,7 @@
       <c r="AH98" s="19"/>
       <c r="AI98" s="19"/>
     </row>
-    <row r="99" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="45"/>
       <c r="B99" s="45"/>
       <c r="F99" s="17" t="s">
@@ -5232,35 +5232,35 @@
       <c r="AF99" s="45"/>
       <c r="AG99" s="45"/>
     </row>
-    <row r="100" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F100" s="46"/>
       <c r="G100" s="36" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="101" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="101" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F101" s="46"/>
       <c r="G101" s="36"/>
     </row>
-    <row r="102" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F102" s="46"/>
       <c r="G102" s="36" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="103" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="103" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F103" s="46"/>
       <c r="G103" s="36" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="104" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="104" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="45"/>
       <c r="B104" s="45"/>
       <c r="AF104" s="45"/>
       <c r="AG104" s="45"/>
     </row>
-    <row r="105" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F105" s="46" t="s">
         <v>162</v>
       </c>
@@ -5268,35 +5268,35 @@
         <v>166</v>
       </c>
     </row>
-    <row r="106" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G106" s="45" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="107" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G107" s="45" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="108" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D108" s="15"/>
       <c r="E108" s="15"/>
       <c r="G108" s="45" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="109" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D109" s="15"/>
       <c r="E109" s="15"/>
       <c r="G109" s="45" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D110" s="15"/>
       <c r="E110" s="15"/>
     </row>
-    <row r="111" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D111" s="46" t="str">
         <f>$C$7&amp;"3."</f>
         <v>7.13.3.</v>
@@ -5305,7 +5305,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="112" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E112" s="30" t="str">
         <f>$D$111&amp;"1."</f>
         <v>7.13.3.1.</v>
@@ -5314,7 +5314,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="113" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E113" s="30"/>
       <c r="F113" s="46" t="s">
         <v>12</v>
@@ -5323,7 +5323,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="114" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E114" s="30"/>
       <c r="F114" s="31"/>
       <c r="G114" s="27" t="s">
@@ -5364,7 +5364,7 @@
       <c r="AH114" s="28"/>
       <c r="AI114" s="29"/>
     </row>
-    <row r="115" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E115" s="30"/>
       <c r="F115" s="31"/>
       <c r="G115" s="23" t="s">
@@ -5405,7 +5405,7 @@
       <c r="AH115" s="24"/>
       <c r="AI115" s="25"/>
     </row>
-    <row r="116" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E116" s="30"/>
       <c r="F116" s="31"/>
       <c r="G116" s="40"/>
@@ -5440,7 +5440,7 @@
       <c r="AH116" s="41"/>
       <c r="AI116" s="42"/>
     </row>
-    <row r="117" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E117" s="30"/>
       <c r="F117" s="31"/>
       <c r="G117" s="19"/>
@@ -5473,7 +5473,7 @@
       <c r="AH117" s="19"/>
       <c r="AI117" s="19"/>
     </row>
-    <row r="118" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E118" s="30"/>
       <c r="F118" s="46" t="s">
         <v>56</v>
@@ -5482,7 +5482,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="119" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E119" s="30"/>
       <c r="F119" s="46"/>
       <c r="G119" s="30" t="str">
@@ -5493,12 +5493,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E120" s="30"/>
       <c r="F120" s="30"/>
       <c r="G120" s="46"/>
       <c r="H120" s="23" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I120" s="24"/>
       <c r="J120" s="24"/>
@@ -5528,12 +5528,12 @@
       <c r="AH120" s="24"/>
       <c r="AI120" s="25"/>
     </row>
-    <row r="121" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E121" s="30"/>
       <c r="F121" s="30"/>
       <c r="G121" s="46"/>
       <c r="H121" s="40" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I121" s="41"/>
       <c r="J121" s="41"/>
@@ -5563,7 +5563,7 @@
       <c r="AH121" s="41"/>
       <c r="AI121" s="42"/>
     </row>
-    <row r="122" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E122" s="30"/>
       <c r="F122" s="30"/>
       <c r="G122" s="46"/>
@@ -5571,7 +5571,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="123" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E123" s="30"/>
       <c r="F123" s="30"/>
       <c r="G123" s="46"/>
@@ -5579,11 +5579,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="124" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E124" s="30"/>
       <c r="F124" s="46"/>
     </row>
-    <row r="125" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E125" s="30"/>
       <c r="F125" s="46"/>
       <c r="G125" s="30" t="str">
@@ -5594,7 +5594,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E126" s="30"/>
       <c r="F126" s="46"/>
       <c r="G126" s="30"/>
@@ -5633,7 +5633,7 @@
       <c r="AH126" s="28"/>
       <c r="AI126" s="29"/>
     </row>
-    <row r="127" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E127" s="30"/>
       <c r="F127" s="46"/>
       <c r="G127" s="30"/>
@@ -5672,7 +5672,7 @@
       <c r="AH127" s="19"/>
       <c r="AI127" s="20"/>
     </row>
-    <row r="128" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E128" s="30"/>
       <c r="F128" s="46"/>
       <c r="G128" s="30"/>
@@ -5711,7 +5711,7 @@
       <c r="AH128" s="43"/>
       <c r="AI128" s="44"/>
     </row>
-    <row r="129" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E129" s="30"/>
       <c r="F129" s="46"/>
       <c r="G129" s="30"/>
@@ -5750,7 +5750,7 @@
       <c r="AH129" s="19"/>
       <c r="AI129" s="20"/>
     </row>
-    <row r="130" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E130" s="30"/>
       <c r="F130" s="46"/>
       <c r="G130" s="30"/>
@@ -5785,7 +5785,7 @@
       <c r="AH130" s="19"/>
       <c r="AI130" s="20"/>
     </row>
-    <row r="131" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E131" s="30"/>
       <c r="F131" s="46"/>
       <c r="G131" s="30"/>
@@ -5820,7 +5820,7 @@
       <c r="AH131" s="41"/>
       <c r="AI131" s="42"/>
     </row>
-    <row r="132" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E132" s="30"/>
       <c r="F132" s="46"/>
       <c r="G132" s="30"/>
@@ -5859,7 +5859,7 @@
       <c r="AH132" s="41"/>
       <c r="AI132" s="42"/>
     </row>
-    <row r="133" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E133" s="30"/>
       <c r="F133" s="46"/>
       <c r="G133" s="30"/>
@@ -5898,7 +5898,7 @@
       <c r="AH133" s="19"/>
       <c r="AI133" s="20"/>
     </row>
-    <row r="134" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E134" s="30"/>
       <c r="F134" s="46"/>
       <c r="G134" s="30"/>
@@ -5933,7 +5933,7 @@
       <c r="AH134" s="19"/>
       <c r="AI134" s="20"/>
     </row>
-    <row r="135" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E135" s="30"/>
       <c r="F135" s="46"/>
       <c r="G135" s="30"/>
@@ -5970,7 +5970,7 @@
       <c r="AH135" s="19"/>
       <c r="AI135" s="20"/>
     </row>
-    <row r="136" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E136" s="30"/>
       <c r="F136" s="46"/>
       <c r="G136" s="30"/>
@@ -6007,7 +6007,7 @@
       <c r="AH136" s="19"/>
       <c r="AI136" s="20"/>
     </row>
-    <row r="137" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E137" s="30"/>
       <c r="F137" s="46"/>
       <c r="H137" s="18"/>
@@ -6043,7 +6043,7 @@
       <c r="AH137" s="19"/>
       <c r="AI137" s="20"/>
     </row>
-    <row r="138" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E138" s="30"/>
       <c r="F138" s="46"/>
       <c r="H138" s="40"/>
@@ -6075,7 +6075,7 @@
       <c r="AH138" s="41"/>
       <c r="AI138" s="42"/>
     </row>
-    <row r="139" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E139" s="30"/>
       <c r="F139" s="46"/>
       <c r="H139" s="40" t="s">
@@ -6113,7 +6113,7 @@
       <c r="AH139" s="41"/>
       <c r="AI139" s="42"/>
     </row>
-    <row r="140" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E140" s="30"/>
       <c r="F140" s="31"/>
       <c r="H140" s="40" t="s">
@@ -6151,7 +6151,7 @@
       <c r="AH140" s="41"/>
       <c r="AI140" s="42"/>
     </row>
-    <row r="141" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E141" s="30"/>
       <c r="H141" s="23" t="s">
         <v>134</v>
@@ -6188,7 +6188,7 @@
       <c r="AH141" s="24"/>
       <c r="AI141" s="25"/>
     </row>
-    <row r="142" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E142" s="30"/>
       <c r="H142" s="40"/>
       <c r="I142" s="41"/>
@@ -6222,8 +6222,8 @@
       <c r="AH142" s="41"/>
       <c r="AI142" s="42"/>
     </row>
-    <row r="143" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E144" s="30"/>
       <c r="F144" s="46" t="s">
         <v>15</v>
@@ -6232,7 +6232,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E145" s="30"/>
       <c r="F145" s="46"/>
       <c r="G145" s="47" t="s">
@@ -6267,7 +6267,7 @@
       <c r="AH145" s="24"/>
       <c r="AI145" s="25"/>
     </row>
-    <row r="146" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E146" s="30"/>
       <c r="F146" s="46"/>
       <c r="G146" s="48" t="s">
@@ -6302,7 +6302,7 @@
       <c r="AH146" s="19"/>
       <c r="AI146" s="20"/>
     </row>
-    <row r="147" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E147" s="30"/>
       <c r="F147" s="46"/>
       <c r="G147" s="48" t="s">
@@ -6337,7 +6337,7 @@
       <c r="AH147" s="19"/>
       <c r="AI147" s="20"/>
     </row>
-    <row r="148" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E148" s="30"/>
       <c r="F148" s="46"/>
       <c r="G148" s="48" t="s">
@@ -6372,7 +6372,7 @@
       <c r="AH148" s="19"/>
       <c r="AI148" s="20"/>
     </row>
-    <row r="149" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E149" s="30"/>
       <c r="F149" s="46"/>
       <c r="G149" s="49" t="s">
@@ -6407,7 +6407,7 @@
       <c r="AH149" s="41"/>
       <c r="AI149" s="42"/>
     </row>
-    <row r="150" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E150" s="30"/>
       <c r="F150" s="46"/>
       <c r="G150" s="50"/>
@@ -6440,7 +6440,7 @@
       <c r="AH150" s="19"/>
       <c r="AI150" s="19"/>
     </row>
-    <row r="151" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E151" s="30" t="str">
         <f>$D$111&amp;"2."</f>
         <v>7.13.3.2.</v>
@@ -6449,7 +6449,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="152" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E152" s="30"/>
       <c r="F152" s="46" t="s">
         <v>12</v>
@@ -6458,7 +6458,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="153" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E153" s="30"/>
       <c r="F153" s="31"/>
       <c r="G153" s="27" t="s">
@@ -6499,7 +6499,7 @@
       <c r="AH153" s="28"/>
       <c r="AI153" s="29"/>
     </row>
-    <row r="154" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E154" s="30"/>
       <c r="F154" s="31"/>
       <c r="G154" s="32" t="s">
@@ -6540,7 +6540,7 @@
       <c r="AH154" s="43"/>
       <c r="AI154" s="44"/>
     </row>
-    <row r="155" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E155" s="30"/>
       <c r="F155" s="31"/>
       <c r="G155" s="18" t="s">
@@ -6581,7 +6581,7 @@
       <c r="AH155" s="19"/>
       <c r="AI155" s="20"/>
     </row>
-    <row r="156" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E156" s="30"/>
       <c r="F156" s="31"/>
       <c r="G156" s="40"/>
@@ -6616,7 +6616,7 @@
       <c r="AH156" s="41"/>
       <c r="AI156" s="42"/>
     </row>
-    <row r="157" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E157" s="30"/>
       <c r="F157" s="31"/>
       <c r="G157" s="32" t="s">
@@ -6657,7 +6657,7 @@
       <c r="AH157" s="43"/>
       <c r="AI157" s="44"/>
     </row>
-    <row r="158" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E158" s="30"/>
       <c r="F158" s="31"/>
       <c r="G158" s="32" t="s">
@@ -6698,11 +6698,11 @@
       <c r="AH158" s="43"/>
       <c r="AI158" s="44"/>
     </row>
-    <row r="159" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E159" s="30"/>
       <c r="F159" s="31"/>
     </row>
-    <row r="160" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E160" s="30"/>
       <c r="F160" s="46" t="s">
         <v>56</v>
@@ -6711,7 +6711,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="161" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E161" s="30"/>
       <c r="F161" s="46"/>
       <c r="G161" s="30" t="str">
@@ -6722,7 +6722,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D162" s="19"/>
       <c r="E162" s="37"/>
       <c r="F162" s="37"/>
@@ -6758,7 +6758,7 @@
       <c r="AH162" s="24"/>
       <c r="AI162" s="25"/>
     </row>
-    <row r="163" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E163" s="30"/>
       <c r="F163" s="30"/>
       <c r="G163" s="46"/>
@@ -6793,7 +6793,7 @@
       <c r="AH163" s="41"/>
       <c r="AI163" s="42"/>
     </row>
-    <row r="164" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E164" s="30"/>
       <c r="F164" s="30"/>
       <c r="G164" s="46"/>
@@ -6801,7 +6801,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="165" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E165" s="30"/>
       <c r="F165" s="30"/>
       <c r="G165" s="46"/>
@@ -6809,11 +6809,11 @@
         <v>122</v>
       </c>
     </row>
-    <row r="166" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E166" s="30"/>
       <c r="F166" s="46"/>
     </row>
-    <row r="167" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E167" s="30"/>
       <c r="F167" s="46"/>
       <c r="G167" s="30" t="str">
@@ -6824,7 +6824,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="168" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E168" s="30"/>
       <c r="F168" s="46"/>
       <c r="G168" s="30"/>
@@ -6863,7 +6863,7 @@
       <c r="AH168" s="28"/>
       <c r="AI168" s="29"/>
     </row>
-    <row r="169" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E169" s="30"/>
       <c r="H169" s="32" t="s">
         <v>78</v>
@@ -6900,7 +6900,7 @@
       <c r="AH169" s="43"/>
       <c r="AI169" s="44"/>
     </row>
-    <row r="170" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E170" s="30"/>
       <c r="H170" s="18" t="s">
         <v>17</v>
@@ -6937,7 +6937,7 @@
       <c r="AH170" s="19"/>
       <c r="AI170" s="20"/>
     </row>
-    <row r="171" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E171" s="30"/>
       <c r="H171" s="40"/>
       <c r="I171" s="41"/>
@@ -6970,7 +6970,7 @@
       <c r="AH171" s="41"/>
       <c r="AI171" s="42"/>
     </row>
-    <row r="172" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E172" s="30"/>
       <c r="H172" s="40" t="s">
         <v>106</v>
@@ -7007,7 +7007,7 @@
       <c r="AH172" s="41"/>
       <c r="AI172" s="42"/>
     </row>
-    <row r="173" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E173" s="30"/>
       <c r="H173" s="40" t="s">
         <v>82</v>
@@ -7044,7 +7044,7 @@
       <c r="AH173" s="41"/>
       <c r="AI173" s="42"/>
     </row>
-    <row r="174" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E174" s="30"/>
       <c r="H174" s="32" t="s">
         <v>123</v>
@@ -7081,7 +7081,7 @@
       <c r="AH174" s="43"/>
       <c r="AI174" s="44"/>
     </row>
-    <row r="175" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E175" s="30"/>
       <c r="H175" s="40" t="s">
         <v>90</v>
@@ -7118,7 +7118,7 @@
       <c r="AH175" s="41"/>
       <c r="AI175" s="42"/>
     </row>
-    <row r="176" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E176" s="30"/>
       <c r="H176" s="40" t="s">
         <v>94</v>
@@ -7155,7 +7155,7 @@
       <c r="AH176" s="41"/>
       <c r="AI176" s="42"/>
     </row>
-    <row r="177" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E177" s="30"/>
       <c r="H177" s="40" t="s">
         <v>96</v>
@@ -7192,7 +7192,7 @@
       <c r="AH177" s="41"/>
       <c r="AI177" s="42"/>
     </row>
-    <row r="178" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E178" s="30"/>
       <c r="H178" s="23" t="s">
         <v>98</v>
@@ -7229,7 +7229,7 @@
       <c r="AH178" s="24"/>
       <c r="AI178" s="25"/>
     </row>
-    <row r="179" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E179" s="30"/>
       <c r="H179" s="40"/>
       <c r="I179" s="41"/>
@@ -7263,7 +7263,7 @@
       <c r="AH179" s="41"/>
       <c r="AI179" s="42"/>
     </row>
-    <row r="180" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E180" s="30"/>
       <c r="H180" s="23" t="s">
         <v>126</v>
@@ -7280,7 +7280,7 @@
       <c r="P180" s="24"/>
       <c r="Q180" s="25"/>
       <c r="R180" s="23" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="S180" s="24"/>
       <c r="T180" s="24"/>
@@ -7300,7 +7300,7 @@
       <c r="AH180" s="24"/>
       <c r="AI180" s="25"/>
     </row>
-    <row r="181" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E181" s="30"/>
       <c r="H181" s="40"/>
       <c r="I181" s="41"/>
@@ -7313,7 +7313,7 @@
       <c r="P181" s="41"/>
       <c r="Q181" s="42"/>
       <c r="R181" s="40" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="S181" s="41"/>
       <c r="T181" s="41"/>
@@ -7333,7 +7333,7 @@
       <c r="AH181" s="41"/>
       <c r="AI181" s="42"/>
     </row>
-    <row r="182" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E182" s="30"/>
       <c r="H182" s="18" t="s">
         <v>128</v>
@@ -7370,7 +7370,7 @@
       <c r="AH182" s="19"/>
       <c r="AI182" s="20"/>
     </row>
-    <row r="183" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E183" s="30"/>
       <c r="H183" s="40"/>
       <c r="I183" s="41"/>
@@ -7403,7 +7403,7 @@
       <c r="AH183" s="41"/>
       <c r="AI183" s="42"/>
     </row>
-    <row r="184" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E184" s="30"/>
       <c r="H184" s="19"/>
       <c r="I184" s="19"/>
@@ -7434,7 +7434,7 @@
       <c r="AH184" s="19"/>
       <c r="AI184" s="19"/>
     </row>
-    <row r="185" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E185" s="30"/>
       <c r="F185" s="46" t="s">
         <v>15</v>
@@ -7443,14 +7443,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="186" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E186" s="30"/>
       <c r="F186" s="46"/>
       <c r="G186" s="45" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="187" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E187" s="30"/>
       <c r="F187" s="46"/>
       <c r="G187" s="47" t="s">
@@ -7485,7 +7485,7 @@
       <c r="AH187" s="24"/>
       <c r="AI187" s="25"/>
     </row>
-    <row r="188" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E188" s="30"/>
       <c r="F188" s="46"/>
       <c r="G188" s="49" t="s">
@@ -7520,7 +7520,7 @@
       <c r="AH188" s="41"/>
       <c r="AI188" s="42"/>
     </row>
-    <row r="189" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E189" s="30"/>
       <c r="F189" s="46"/>
       <c r="G189" s="50"/>
@@ -7553,7 +7553,7 @@
       <c r="AH189" s="19"/>
       <c r="AI189" s="19"/>
     </row>
-    <row r="190" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E190" s="30"/>
       <c r="F190" s="46"/>
       <c r="G190" s="50"/>
@@ -7586,7 +7586,7 @@
       <c r="AH190" s="19"/>
       <c r="AI190" s="19"/>
     </row>
-    <row r="191" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="45"/>
       <c r="B191" s="45"/>
       <c r="D191" s="46" t="str">
@@ -7599,23 +7599,23 @@
       <c r="AF191" s="45"/>
       <c r="AG191" s="45"/>
     </row>
-    <row r="192" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D192" s="46"/>
       <c r="E192" s="31" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="193" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="193" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D193" s="46"/>
       <c r="E193" s="31" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="194" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D194" s="46"/>
       <c r="E194" s="31"/>
     </row>
-    <row r="195" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D195" s="46"/>
       <c r="E195" s="27" t="s">
         <v>10</v>
@@ -7650,7 +7650,7 @@
       <c r="AE195" s="28"/>
       <c r="AF195" s="29"/>
     </row>
-    <row r="196" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="196" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D196" s="46"/>
       <c r="E196" s="58" t="s">
         <v>37</v>
@@ -7660,7 +7660,7 @@
       <c r="H196" s="24"/>
       <c r="I196" s="25"/>
       <c r="J196" s="59" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="K196" s="59"/>
       <c r="L196" s="59"/>
@@ -7685,7 +7685,7 @@
       <c r="AE196" s="59"/>
       <c r="AF196" s="60"/>
     </row>
-    <row r="197" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="197" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D197" s="46"/>
       <c r="E197" s="57"/>
       <c r="F197" s="41"/>
@@ -7716,7 +7716,7 @@
       <c r="AE197" s="61"/>
       <c r="AF197" s="62"/>
     </row>
-    <row r="198" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="198" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D198" s="46"/>
       <c r="E198" s="58" t="s">
         <v>39</v>
@@ -7726,7 +7726,7 @@
       <c r="H198" s="24"/>
       <c r="I198" s="25"/>
       <c r="J198" s="59" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="K198" s="59"/>
       <c r="L198" s="59"/>
@@ -7751,7 +7751,7 @@
       <c r="AE198" s="59"/>
       <c r="AF198" s="60"/>
     </row>
-    <row r="199" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="199" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D199" s="46"/>
       <c r="E199" s="57"/>
       <c r="F199" s="41"/>
@@ -7782,7 +7782,7 @@
       <c r="AE199" s="61"/>
       <c r="AF199" s="62"/>
     </row>
-    <row r="200" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="200" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D200" s="46"/>
       <c r="E200" s="58" t="s">
         <v>41</v>
@@ -7792,7 +7792,7 @@
       <c r="H200" s="24"/>
       <c r="I200" s="25"/>
       <c r="J200" s="59" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="K200" s="59"/>
       <c r="L200" s="59"/>
@@ -7817,7 +7817,7 @@
       <c r="AE200" s="59"/>
       <c r="AF200" s="60"/>
     </row>
-    <row r="201" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="201" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D201" s="46"/>
       <c r="E201" s="57"/>
       <c r="F201" s="41"/>
@@ -7848,7 +7848,7 @@
       <c r="AE201" s="61"/>
       <c r="AF201" s="62"/>
     </row>
-    <row r="202" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="202" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D202" s="46"/>
       <c r="E202" s="58" t="s">
         <v>44</v>
@@ -7858,7 +7858,7 @@
       <c r="H202" s="24"/>
       <c r="I202" s="25"/>
       <c r="J202" s="63" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="K202" s="59"/>
       <c r="L202" s="59"/>
@@ -7883,7 +7883,7 @@
       <c r="AE202" s="59"/>
       <c r="AF202" s="60"/>
     </row>
-    <row r="203" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="203" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D203" s="46"/>
       <c r="E203" s="57"/>
       <c r="F203" s="41"/>
@@ -7914,46 +7914,46 @@
       <c r="AE203" s="61"/>
       <c r="AF203" s="62"/>
     </row>
-    <row r="204" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E205" s="45" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="206" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="206" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E207" s="31" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="208" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="208" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E208" s="31" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="209" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="209" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E210" s="46" t="str">
         <f>$D$191&amp;"1."</f>
         <v>7.13.4.1.</v>
       </c>
       <c r="F210" s="45" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="211" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="211" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E211" s="46"/>
       <c r="F211" s="30" t="str">
         <f>$E$210&amp;"1."</f>
         <v>7.13.4.1.1.</v>
       </c>
       <c r="G211" s="45" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="212" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="212" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G212" s="23" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H212" s="24"/>
       <c r="I212" s="24"/>
@@ -7983,15 +7983,15 @@
       <c r="AG212" s="24"/>
       <c r="AH212" s="25"/>
     </row>
-    <row r="213" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G213" s="18" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AH213" s="20"/>
     </row>
-    <row r="214" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G214" s="40" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H214" s="41"/>
       <c r="I214" s="41"/>
@@ -8021,48 +8021,48 @@
       <c r="AG214" s="41"/>
       <c r="AH214" s="42"/>
     </row>
-    <row r="215" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="215" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G215" s="36" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="216" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="216" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G216" s="45" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="217" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="217" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G217" s="36" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="218" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="218" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D218" s="46"/>
       <c r="E218" s="31"/>
     </row>
-    <row r="219" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="219" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E219" s="46" t="str">
         <f>$D$191&amp;"2."</f>
         <v>7.13.4.2.</v>
       </c>
       <c r="F219" s="45" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="220" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="220" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E220" s="46"/>
       <c r="F220" s="30" t="str">
         <f>$E$219&amp;"1."</f>
         <v>7.13.4.2.1.</v>
       </c>
       <c r="G220" s="45" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="221" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="221" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E221" s="30"/>
       <c r="G221" s="39" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H221" s="24"/>
       <c r="I221" s="24"/>
@@ -8092,45 +8092,45 @@
       <c r="AG221" s="24"/>
       <c r="AH221" s="25"/>
     </row>
-    <row r="222" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E222" s="30"/>
       <c r="G222" s="18" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AH222" s="20"/>
     </row>
-    <row r="223" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E223" s="30"/>
       <c r="G223" s="18" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AH223" s="20"/>
     </row>
-    <row r="224" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E224" s="30"/>
       <c r="G224" s="18" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AH224" s="20"/>
     </row>
-    <row r="225" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E225" s="30"/>
       <c r="G225" s="18" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AH225" s="20"/>
     </row>
-    <row r="226" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E226" s="30"/>
       <c r="G226" s="18" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AH226" s="20"/>
     </row>
-    <row r="227" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E227" s="30"/>
       <c r="G227" s="40" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H227" s="41"/>
       <c r="I227" s="41"/>
@@ -8160,18 +8160,18 @@
       <c r="AG227" s="41"/>
       <c r="AH227" s="42"/>
     </row>
-    <row r="228" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G228" s="36" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="229" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G229" s="45" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="230" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="230" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E231" s="30"/>
       <c r="F231" s="46"/>
       <c r="G231" s="50"/>
@@ -8204,7 +8204,7 @@
       <c r="AH231" s="19"/>
       <c r="AI231" s="19"/>
     </row>
-    <row r="232" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="45"/>
       <c r="B232" s="45"/>
       <c r="D232" s="46" t="str">
@@ -8218,7 +8218,7 @@
       <c r="AF232" s="45"/>
       <c r="AG232" s="45"/>
     </row>
-    <row r="233" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="45"/>
       <c r="B233" s="45"/>
       <c r="E233" s="31" t="s">
@@ -8228,50 +8228,50 @@
       <c r="AF233" s="45"/>
       <c r="AG233" s="45"/>
     </row>
-    <row r="234" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="45"/>
       <c r="B234" s="45"/>
       <c r="E234" s="30"/>
       <c r="AF234" s="45"/>
       <c r="AG234" s="45"/>
     </row>
-    <row r="235" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AF235" s="45"/>
       <c r="AG235" s="45"/>
     </row>
-    <row r="236" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="46" t="str">
         <f>$C$7&amp;"6."</f>
         <v>7.13.6.</v>
       </c>
       <c r="E236" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="237" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E237" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="238" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E238" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="240" spans="1:35" s="45" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E240" s="45" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="237" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E237" s="4" t="s">
+    <row r="241" spans="5:5" s="45" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" spans="5:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E242" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="244" spans="5:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E244" s="4" t="s">
         <v>264</v>
-      </c>
-    </row>
-    <row r="238" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E238" s="4" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="240" spans="1:35" s="45" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E240" s="45" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="241" spans="5:5" s="45" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" spans="5:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E242" s="4" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="244" spans="5:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E244" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.13ログ.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.13ログ.xlsx
@@ -2,13 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\t-uchida\projects\github.com\Fintan-contents\application-architecture-sample\nablarch_sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FB4906-BC06-47F9-AC8E-5550FF0DA748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B72A41-DEEE-4B71-9A54-CA30BCCD45FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.13ログ.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.13ログ.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\gitbucket\Fintan\application-architecture-sample\nablarch_sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4157B466-4D97-4793-9BC8-D97C3572D049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B72A41-DEEE-4B71-9A54-CA30BCCD45FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.13.ログ" sheetId="2" r:id="rId1"/>
@@ -1129,22 +1124,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/log/failure_log.html#failure-log-setting</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/log/sql_log.html#sql-log-setting</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/log/http_access_log.html#http-access-log-setting</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://nablarch.github.io/docs/LATEST/doc/application_framework/application_framework/libraries/log/performance_log.html#performance-log-setting</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>※実行状況ログについては、フォーマットの指定はできないためNablarchが出力するものをそのまま使用する。</t>
     <rPh sb="20" eb="22">
       <t>シテイ</t>
@@ -1509,6 +1488,22 @@
     <rPh sb="52" eb="54">
       <t>シヨウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/log/failure_log.html#failure-log-setting</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/log/http_access_log.html#http-access-log-setting</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/log/sql_log.html#sql-log-setting</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/log/performance_log.html#performance-log-setting</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1582,7 +1577,7 @@
       <sz val="9"/>
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -2353,13 +2348,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AS244"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="3.625" style="45"/>
-    <col min="3" max="16384" width="3.625" style="4"/>
+    <col min="1" max="2" width="3.6328125" style="45"/>
+    <col min="3" max="16384" width="3.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>140</v>
       </c>
@@ -2404,7 +2399,7 @@
       <c r="AH1" s="75"/>
       <c r="AI1" s="76"/>
     </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -2449,7 +2444,7 @@
       <c r="AH2" s="75"/>
       <c r="AI2" s="76"/>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2490,8 +2485,8 @@
       <c r="AH3" s="75"/>
       <c r="AI3" s="76"/>
     </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="46" t="s">
         <v>155</v>
       </c>
@@ -2499,8 +2494,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="46" t="str">
         <f>$B$5&amp;"13."</f>
         <v>7.13.</v>
@@ -2509,17 +2504,17 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="46"/>
       <c r="D8" s="45" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AF9" s="45"/>
       <c r="AG9" s="45"/>
     </row>
-    <row r="10" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45"/>
       <c r="B10" s="45"/>
       <c r="D10" s="17" t="str">
@@ -2532,7 +2527,7 @@
       <c r="AF10" s="45"/>
       <c r="AG10" s="45"/>
     </row>
-    <row r="11" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="45"/>
       <c r="B11" s="45"/>
       <c r="D11" s="17"/>
@@ -2546,7 +2541,7 @@
       <c r="AF11" s="45"/>
       <c r="AG11" s="45"/>
     </row>
-    <row r="12" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45"/>
       <c r="B12" s="45"/>
       <c r="D12" s="17"/>
@@ -2557,7 +2552,7 @@
       <c r="AF12" s="45"/>
       <c r="AG12" s="45"/>
     </row>
-    <row r="13" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45"/>
       <c r="B13" s="45"/>
       <c r="D13" s="17"/>
@@ -2599,7 +2594,7 @@
       <c r="AH13" s="55"/>
       <c r="AI13" s="56"/>
     </row>
-    <row r="14" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="46"/>
       <c r="E14" s="46"/>
       <c r="F14" s="51"/>
@@ -2635,7 +2630,7 @@
       <c r="AH14" s="52"/>
       <c r="AI14" s="53"/>
     </row>
-    <row r="15" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="45"/>
       <c r="B15" s="45"/>
       <c r="D15" s="17"/>
@@ -2677,7 +2672,7 @@
       <c r="AH15" s="24"/>
       <c r="AI15" s="25"/>
     </row>
-    <row r="16" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="46"/>
       <c r="E16" s="46"/>
       <c r="F16" s="35"/>
@@ -2713,7 +2708,7 @@
       <c r="AH16" s="41"/>
       <c r="AI16" s="42"/>
     </row>
-    <row r="17" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="45"/>
       <c r="B17" s="45"/>
       <c r="D17" s="17"/>
@@ -2755,7 +2750,7 @@
       <c r="AH17" s="19"/>
       <c r="AI17" s="20"/>
     </row>
-    <row r="18" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45"/>
       <c r="B18" s="45"/>
       <c r="D18" s="17"/>
@@ -2793,7 +2788,7 @@
       <c r="AH18" s="22"/>
       <c r="AI18" s="26"/>
     </row>
-    <row r="19" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="45"/>
       <c r="B19" s="45"/>
       <c r="D19" s="17"/>
@@ -2836,7 +2831,7 @@
       <c r="AI19" s="20"/>
       <c r="AK19" s="45"/>
     </row>
-    <row r="20" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45"/>
       <c r="B20" s="45"/>
       <c r="D20" s="17"/>
@@ -2875,7 +2870,7 @@
       <c r="AI20" s="20"/>
       <c r="AK20" s="45"/>
     </row>
-    <row r="21" spans="1:37" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:37" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D21" s="46"/>
       <c r="E21" s="46"/>
       <c r="F21" s="40"/>
@@ -2911,7 +2906,7 @@
       <c r="AH21" s="41"/>
       <c r="AI21" s="42"/>
     </row>
-    <row r="22" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45"/>
       <c r="B22" s="45"/>
       <c r="D22" s="17"/>
@@ -2953,7 +2948,7 @@
       <c r="AH22" s="19"/>
       <c r="AI22" s="20"/>
     </row>
-    <row r="23" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="D23" s="17"/>
@@ -2989,7 +2984,7 @@
       <c r="AH23" s="22"/>
       <c r="AI23" s="26"/>
     </row>
-    <row r="24" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="45"/>
       <c r="B24" s="45"/>
       <c r="D24" s="17"/>
@@ -3031,7 +3026,7 @@
       <c r="AH24" s="19"/>
       <c r="AI24" s="20"/>
     </row>
-    <row r="25" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="45"/>
       <c r="B25" s="45"/>
       <c r="D25" s="17"/>
@@ -3067,7 +3062,7 @@
       <c r="AH25" s="22"/>
       <c r="AI25" s="26"/>
     </row>
-    <row r="26" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="45"/>
       <c r="B26" s="45"/>
       <c r="D26" s="17"/>
@@ -3109,7 +3104,7 @@
       <c r="AH26" s="19"/>
       <c r="AI26" s="20"/>
     </row>
-    <row r="27" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="45"/>
       <c r="B27" s="45"/>
       <c r="D27" s="17"/>
@@ -3145,7 +3140,7 @@
       <c r="AH27" s="22"/>
       <c r="AI27" s="26"/>
     </row>
-    <row r="28" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="45"/>
       <c r="B28" s="45"/>
       <c r="D28" s="17"/>
@@ -3153,7 +3148,7 @@
       <c r="AE28" s="45"/>
       <c r="AF28" s="45"/>
     </row>
-    <row r="29" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="45"/>
       <c r="B29" s="45"/>
       <c r="D29" s="17"/>
@@ -3164,7 +3159,7 @@
       <c r="AE29" s="45"/>
       <c r="AF29" s="45"/>
     </row>
-    <row r="30" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="45"/>
       <c r="B30" s="45"/>
       <c r="D30" s="17"/>
@@ -3206,7 +3201,7 @@
       <c r="AH30" s="28"/>
       <c r="AI30" s="29"/>
     </row>
-    <row r="31" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="45"/>
       <c r="B31" s="45"/>
       <c r="D31" s="38"/>
@@ -3249,7 +3244,7 @@
       <c r="AH31" s="43"/>
       <c r="AI31" s="44"/>
     </row>
-    <row r="32" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:37" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="45"/>
       <c r="B32" s="45"/>
       <c r="D32" s="17"/>
@@ -3292,7 +3287,7 @@
       <c r="AH32" s="43"/>
       <c r="AI32" s="44"/>
     </row>
-    <row r="33" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="45"/>
       <c r="B33" s="45"/>
       <c r="D33" s="17"/>
@@ -3335,7 +3330,7 @@
       <c r="AH33" s="43"/>
       <c r="AI33" s="44"/>
     </row>
-    <row r="34" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="45"/>
       <c r="B34" s="45"/>
       <c r="D34" s="17"/>
@@ -3378,7 +3373,7 @@
       <c r="AH34" s="43"/>
       <c r="AI34" s="44"/>
     </row>
-    <row r="35" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="45"/>
       <c r="B35" s="45"/>
       <c r="D35" s="17"/>
@@ -3421,7 +3416,7 @@
       <c r="AH35" s="24"/>
       <c r="AI35" s="25"/>
     </row>
-    <row r="36" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D36" s="46"/>
       <c r="E36" s="46"/>
       <c r="F36" s="40"/>
@@ -3459,7 +3454,7 @@
       <c r="AH36" s="41"/>
       <c r="AI36" s="42"/>
     </row>
-    <row r="37" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="45"/>
       <c r="B37" s="45"/>
       <c r="D37" s="17"/>
@@ -3502,7 +3497,7 @@
       <c r="AH37" s="24"/>
       <c r="AI37" s="25"/>
     </row>
-    <row r="38" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D38" s="46"/>
       <c r="E38" s="46"/>
       <c r="F38" s="40"/>
@@ -3554,7 +3549,7 @@
       <c r="AF40" s="45"/>
       <c r="AG40" s="45"/>
     </row>
-    <row r="41" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="45"/>
       <c r="B41" s="45"/>
       <c r="D41" s="17"/>
@@ -3568,7 +3563,7 @@
       <c r="AF41" s="45"/>
       <c r="AG41" s="45"/>
     </row>
-    <row r="42" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="45"/>
       <c r="B42" s="45"/>
       <c r="D42" s="17"/>
@@ -3579,7 +3574,7 @@
       <c r="AF42" s="45"/>
       <c r="AG42" s="45"/>
     </row>
-    <row r="43" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="45"/>
       <c r="B43" s="45"/>
       <c r="F43" s="27" t="s">
@@ -3619,7 +3614,7 @@
       <c r="AH43" s="28"/>
       <c r="AI43" s="29"/>
     </row>
-    <row r="44" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="45"/>
       <c r="B44" s="45"/>
       <c r="F44" s="32" t="s">
@@ -3659,7 +3654,7 @@
       <c r="AH44" s="33"/>
       <c r="AI44" s="34"/>
     </row>
-    <row r="45" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="45"/>
       <c r="B45" s="45"/>
       <c r="F45" s="18" t="s">
@@ -3699,7 +3694,7 @@
       <c r="AH45" s="19"/>
       <c r="AI45" s="20"/>
     </row>
-    <row r="46" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F46" s="18"/>
       <c r="G46" s="19"/>
       <c r="H46" s="19"/>
@@ -3733,7 +3728,7 @@
       <c r="AH46" s="19"/>
       <c r="AI46" s="20"/>
     </row>
-    <row r="47" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="45"/>
       <c r="B47" s="45"/>
       <c r="F47" s="21"/>
@@ -3769,7 +3764,7 @@
       <c r="AH47" s="22"/>
       <c r="AI47" s="26"/>
     </row>
-    <row r="48" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="45"/>
       <c r="B48" s="45"/>
       <c r="F48" s="18" t="s">
@@ -3809,7 +3804,7 @@
       <c r="AH48" s="19"/>
       <c r="AI48" s="20"/>
     </row>
-    <row r="49" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F49" s="18"/>
       <c r="G49" s="19"/>
       <c r="H49" s="19"/>
@@ -3843,7 +3838,7 @@
       <c r="AH49" s="19"/>
       <c r="AI49" s="20"/>
     </row>
-    <row r="50" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="45"/>
       <c r="B50" s="45"/>
       <c r="F50" s="21"/>
@@ -3879,7 +3874,7 @@
       <c r="AH50" s="22"/>
       <c r="AI50" s="26"/>
     </row>
-    <row r="51" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="45"/>
       <c r="B51" s="45"/>
       <c r="F51" s="18" t="s">
@@ -3919,7 +3914,7 @@
       <c r="AH51" s="19"/>
       <c r="AI51" s="20"/>
     </row>
-    <row r="52" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="45"/>
       <c r="B52" s="45"/>
       <c r="F52" s="21"/>
@@ -3955,7 +3950,7 @@
       <c r="AH52" s="22"/>
       <c r="AI52" s="26"/>
     </row>
-    <row r="53" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="45"/>
       <c r="B53" s="45"/>
       <c r="F53" s="18" t="s">
@@ -3995,7 +3990,7 @@
       <c r="AH53" s="19"/>
       <c r="AI53" s="20"/>
     </row>
-    <row r="54" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="45"/>
       <c r="B54" s="45"/>
       <c r="F54" s="18"/>
@@ -4031,7 +4026,7 @@
       <c r="AH54" s="19"/>
       <c r="AI54" s="20"/>
     </row>
-    <row r="55" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="45"/>
       <c r="B55" s="45"/>
       <c r="F55" s="18"/>
@@ -4067,7 +4062,7 @@
       <c r="AH55" s="19"/>
       <c r="AI55" s="20"/>
     </row>
-    <row r="56" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="45"/>
       <c r="B56" s="45"/>
       <c r="F56" s="18"/>
@@ -4103,7 +4098,7 @@
       <c r="AH56" s="19"/>
       <c r="AI56" s="20"/>
     </row>
-    <row r="57" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="45"/>
       <c r="B57" s="45"/>
       <c r="F57" s="18"/>
@@ -4139,7 +4134,7 @@
       <c r="AH57" s="19"/>
       <c r="AI57" s="20"/>
     </row>
-    <row r="58" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="45"/>
       <c r="B58" s="45"/>
       <c r="F58" s="18"/>
@@ -4175,7 +4170,7 @@
       <c r="AH58" s="19"/>
       <c r="AI58" s="20"/>
     </row>
-    <row r="59" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F59" s="18"/>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
@@ -4209,7 +4204,7 @@
       <c r="AH59" s="19"/>
       <c r="AI59" s="20"/>
     </row>
-    <row r="60" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="45"/>
       <c r="B60" s="45"/>
       <c r="F60" s="18"/>
@@ -4245,7 +4240,7 @@
       <c r="AH60" s="19"/>
       <c r="AI60" s="20"/>
     </row>
-    <row r="61" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="45"/>
       <c r="B61" s="45"/>
       <c r="F61" s="18"/>
@@ -4281,7 +4276,7 @@
       <c r="AH61" s="19"/>
       <c r="AI61" s="20"/>
     </row>
-    <row r="62" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="45"/>
       <c r="B62" s="45"/>
       <c r="F62" s="21"/>
@@ -4317,19 +4312,19 @@
       <c r="AH62" s="22"/>
       <c r="AI62" s="26"/>
     </row>
-    <row r="63" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="45"/>
       <c r="B63" s="45"/>
       <c r="AF63" s="45"/>
       <c r="AG63" s="45"/>
     </row>
-    <row r="64" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F64" s="45" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="45"/>
       <c r="B66" s="45"/>
       <c r="F66" s="19"/>
@@ -4364,7 +4359,7 @@
       <c r="AI66" s="19"/>
       <c r="AJ66" s="19"/>
     </row>
-    <row r="67" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="45"/>
       <c r="B67" s="45"/>
       <c r="E67" s="17" t="str">
@@ -4377,7 +4372,7 @@
       <c r="AF67" s="45"/>
       <c r="AG67" s="45"/>
     </row>
-    <row r="68" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="45"/>
       <c r="B68" s="45"/>
       <c r="F68" s="16" t="s">
@@ -4386,13 +4381,13 @@
       <c r="AF68" s="45"/>
       <c r="AG68" s="45"/>
     </row>
-    <row r="69" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="45"/>
       <c r="B69" s="45"/>
       <c r="AF69" s="45"/>
       <c r="AG69" s="45"/>
     </row>
-    <row r="70" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E70" s="46" t="str">
         <f>$D$10&amp;"4."</f>
         <v>7.13.1.4.</v>
@@ -4402,7 +4397,7 @@
       </c>
       <c r="G70" s="30"/>
     </row>
-    <row r="71" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="45"/>
       <c r="B71" s="45"/>
       <c r="E71" s="30"/>
@@ -4420,7 +4415,7 @@
       <c r="AF71" s="45"/>
       <c r="AG71" s="45"/>
     </row>
-    <row r="72" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="45"/>
       <c r="B72" s="45"/>
       <c r="E72" s="30"/>
@@ -4438,7 +4433,7 @@
       <c r="AF72" s="45"/>
       <c r="AG72" s="45"/>
     </row>
-    <row r="73" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="45"/>
       <c r="B73" s="45"/>
       <c r="E73" s="30"/>
@@ -4454,7 +4449,7 @@
       <c r="AF73" s="45"/>
       <c r="AG73" s="45"/>
     </row>
-    <row r="74" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="45"/>
       <c r="B74" s="45"/>
       <c r="E74" s="30"/>
@@ -4497,7 +4492,7 @@
       <c r="AR74" s="45"/>
       <c r="AS74" s="45"/>
     </row>
-    <row r="75" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="45"/>
       <c r="B75" s="45"/>
       <c r="E75" s="30"/>
@@ -4540,7 +4535,7 @@
       <c r="AR75" s="45"/>
       <c r="AS75" s="45"/>
     </row>
-    <row r="76" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:45" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E76" s="30"/>
       <c r="F76" s="40"/>
       <c r="G76" s="41"/>
@@ -4575,7 +4570,7 @@
       <c r="AH76" s="41"/>
       <c r="AI76" s="42"/>
     </row>
-    <row r="77" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="45"/>
       <c r="B77" s="45"/>
       <c r="E77" s="30"/>
@@ -4584,13 +4579,13 @@
       <c r="AF77" s="45"/>
       <c r="AG77" s="45"/>
     </row>
-    <row r="78" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="45"/>
       <c r="B78" s="45"/>
       <c r="AF78" s="45"/>
       <c r="AG78" s="45"/>
     </row>
-    <row r="79" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="45"/>
       <c r="B79" s="45"/>
       <c r="D79" s="46" t="str">
@@ -4603,7 +4598,7 @@
       <c r="AF79" s="45"/>
       <c r="AG79" s="45"/>
     </row>
-    <row r="80" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:45" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="45"/>
       <c r="B80" s="45"/>
       <c r="E80" s="17" t="str">
@@ -4616,7 +4611,7 @@
       <c r="AF80" s="45"/>
       <c r="AG80" s="45"/>
     </row>
-    <row r="81" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="45"/>
       <c r="B81" s="45"/>
       <c r="F81" s="17" t="s">
@@ -4628,17 +4623,17 @@
       <c r="AF81" s="45"/>
       <c r="AG81" s="45"/>
     </row>
-    <row r="82" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="45"/>
       <c r="B82" s="45"/>
       <c r="F82" s="17"/>
       <c r="G82" s="16" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AF82" s="45"/>
       <c r="AG82" s="45"/>
     </row>
-    <row r="83" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="45"/>
       <c r="B83" s="45"/>
       <c r="D83" s="15"/>
@@ -4677,7 +4672,7 @@
       <c r="AH83" s="28"/>
       <c r="AI83" s="29"/>
     </row>
-    <row r="84" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="45"/>
       <c r="B84" s="45"/>
       <c r="D84" s="15"/>
@@ -4716,7 +4711,7 @@
       <c r="AH84" s="43"/>
       <c r="AI84" s="44"/>
     </row>
-    <row r="85" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="45"/>
       <c r="B85" s="45"/>
       <c r="D85" s="15"/>
@@ -4755,23 +4750,23 @@
       <c r="AH85" s="43"/>
       <c r="AI85" s="44"/>
     </row>
-    <row r="86" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="45"/>
       <c r="B86" s="45"/>
       <c r="G86" s="17"/>
       <c r="AF86" s="45"/>
       <c r="AG86" s="45"/>
     </row>
-    <row r="87" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="45"/>
       <c r="B87" s="45"/>
       <c r="G87" s="16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AF87" s="45"/>
       <c r="AG87" s="45"/>
     </row>
-    <row r="88" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="45"/>
       <c r="B88" s="45"/>
       <c r="D88" s="15"/>
@@ -4805,20 +4800,20 @@
       <c r="Y88" s="28"/>
       <c r="Z88" s="29"/>
       <c r="AA88" s="27" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AB88" s="28"/>
       <c r="AC88" s="28"/>
       <c r="AD88" s="28"/>
       <c r="AE88" s="28"/>
       <c r="AF88" s="27" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AG88" s="28"/>
       <c r="AH88" s="28"/>
       <c r="AI88" s="29"/>
     </row>
-    <row r="89" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="45"/>
       <c r="B89" s="45"/>
       <c r="D89" s="15"/>
@@ -4832,7 +4827,7 @@
       <c r="J89" s="24"/>
       <c r="K89" s="24"/>
       <c r="L89" s="23" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M89" s="24"/>
       <c r="N89" s="24"/>
@@ -4866,7 +4861,7 @@
       <c r="AH89" s="24"/>
       <c r="AI89" s="25"/>
     </row>
-    <row r="90" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D90" s="15"/>
       <c r="E90" s="15"/>
       <c r="G90" s="23" t="str">
@@ -4884,7 +4879,7 @@
       <c r="N90" s="24"/>
       <c r="O90" s="24"/>
       <c r="P90" s="23" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="Q90" s="24"/>
       <c r="R90" s="24"/>
@@ -4906,13 +4901,13 @@
       <c r="AD90" s="24"/>
       <c r="AE90" s="24"/>
       <c r="AF90" s="23" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AG90" s="24"/>
       <c r="AH90" s="24"/>
       <c r="AI90" s="25"/>
     </row>
-    <row r="91" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="45"/>
       <c r="B91" s="45"/>
       <c r="D91" s="15"/>
@@ -4926,7 +4921,7 @@
       <c r="J91" s="24"/>
       <c r="K91" s="24"/>
       <c r="L91" s="23" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M91" s="24"/>
       <c r="N91" s="24"/>
@@ -4960,7 +4955,7 @@
       <c r="AH91" s="24"/>
       <c r="AI91" s="25"/>
     </row>
-    <row r="92" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="45"/>
       <c r="B92" s="45"/>
       <c r="D92" s="15"/>
@@ -4997,7 +4992,7 @@
       <c r="AH92" s="19"/>
       <c r="AI92" s="20"/>
     </row>
-    <row r="93" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="45"/>
       <c r="B93" s="45"/>
       <c r="D93" s="15"/>
@@ -5034,7 +5029,7 @@
       <c r="AH93" s="19"/>
       <c r="AI93" s="20"/>
     </row>
-    <row r="94" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D94" s="15"/>
       <c r="E94" s="15"/>
       <c r="G94" s="40"/>
@@ -5069,7 +5064,7 @@
       <c r="AH94" s="41"/>
       <c r="AI94" s="42"/>
     </row>
-    <row r="95" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D95" s="15"/>
       <c r="E95" s="15"/>
       <c r="G95" s="23" t="str">
@@ -5087,7 +5082,7 @@
       <c r="N95" s="24"/>
       <c r="O95" s="24"/>
       <c r="P95" s="23" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Q95" s="24"/>
       <c r="R95" s="24"/>
@@ -5109,13 +5104,13 @@
       <c r="AD95" s="24"/>
       <c r="AE95" s="25"/>
       <c r="AF95" s="23" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AG95" s="24"/>
       <c r="AH95" s="24"/>
       <c r="AI95" s="25"/>
     </row>
-    <row r="96" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D96" s="15"/>
       <c r="E96" s="15"/>
       <c r="G96" s="18"/>
@@ -5150,7 +5145,7 @@
       <c r="AH96" s="19"/>
       <c r="AI96" s="20"/>
     </row>
-    <row r="97" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D97" s="15"/>
       <c r="E97" s="15"/>
       <c r="G97" s="40"/>
@@ -5185,7 +5180,7 @@
       <c r="AH97" s="41"/>
       <c r="AI97" s="42"/>
     </row>
-    <row r="98" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="45"/>
       <c r="B98" s="45"/>
       <c r="D98" s="15"/>
@@ -5220,7 +5215,7 @@
       <c r="AH98" s="19"/>
       <c r="AI98" s="19"/>
     </row>
-    <row r="99" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="45"/>
       <c r="B99" s="45"/>
       <c r="F99" s="17" t="s">
@@ -5232,35 +5227,35 @@
       <c r="AF99" s="45"/>
       <c r="AG99" s="45"/>
     </row>
-    <row r="100" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F100" s="46"/>
       <c r="G100" s="36" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="101" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="101" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F101" s="46"/>
       <c r="G101" s="36"/>
     </row>
-    <row r="102" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F102" s="46"/>
       <c r="G102" s="36" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="103" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="103" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F103" s="46"/>
       <c r="G103" s="36" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="104" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="104" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="45"/>
       <c r="B104" s="45"/>
       <c r="AF104" s="45"/>
       <c r="AG104" s="45"/>
     </row>
-    <row r="105" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F105" s="46" t="s">
         <v>162</v>
       </c>
@@ -5268,35 +5263,35 @@
         <v>166</v>
       </c>
     </row>
-    <row r="106" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G106" s="45" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="107" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G107" s="45" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="108" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D108" s="15"/>
       <c r="E108" s="15"/>
       <c r="G108" s="45" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="109" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D109" s="15"/>
       <c r="E109" s="15"/>
       <c r="G109" s="45" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D110" s="15"/>
       <c r="E110" s="15"/>
     </row>
-    <row r="111" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D111" s="46" t="str">
         <f>$C$7&amp;"3."</f>
         <v>7.13.3.</v>
@@ -5305,7 +5300,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="112" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E112" s="30" t="str">
         <f>$D$111&amp;"1."</f>
         <v>7.13.3.1.</v>
@@ -5314,7 +5309,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="113" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E113" s="30"/>
       <c r="F113" s="46" t="s">
         <v>12</v>
@@ -5323,7 +5318,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="114" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E114" s="30"/>
       <c r="F114" s="31"/>
       <c r="G114" s="27" t="s">
@@ -5364,7 +5359,7 @@
       <c r="AH114" s="28"/>
       <c r="AI114" s="29"/>
     </row>
-    <row r="115" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E115" s="30"/>
       <c r="F115" s="31"/>
       <c r="G115" s="23" t="s">
@@ -5405,7 +5400,7 @@
       <c r="AH115" s="24"/>
       <c r="AI115" s="25"/>
     </row>
-    <row r="116" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E116" s="30"/>
       <c r="F116" s="31"/>
       <c r="G116" s="40"/>
@@ -5440,7 +5435,7 @@
       <c r="AH116" s="41"/>
       <c r="AI116" s="42"/>
     </row>
-    <row r="117" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E117" s="30"/>
       <c r="F117" s="31"/>
       <c r="G117" s="19"/>
@@ -5473,7 +5468,7 @@
       <c r="AH117" s="19"/>
       <c r="AI117" s="19"/>
     </row>
-    <row r="118" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E118" s="30"/>
       <c r="F118" s="46" t="s">
         <v>56</v>
@@ -5482,7 +5477,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="119" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E119" s="30"/>
       <c r="F119" s="46"/>
       <c r="G119" s="30" t="str">
@@ -5493,12 +5488,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E120" s="30"/>
       <c r="F120" s="30"/>
       <c r="G120" s="46"/>
       <c r="H120" s="23" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I120" s="24"/>
       <c r="J120" s="24"/>
@@ -5528,12 +5523,12 @@
       <c r="AH120" s="24"/>
       <c r="AI120" s="25"/>
     </row>
-    <row r="121" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E121" s="30"/>
       <c r="F121" s="30"/>
       <c r="G121" s="46"/>
       <c r="H121" s="40" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I121" s="41"/>
       <c r="J121" s="41"/>
@@ -5563,7 +5558,7 @@
       <c r="AH121" s="41"/>
       <c r="AI121" s="42"/>
     </row>
-    <row r="122" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E122" s="30"/>
       <c r="F122" s="30"/>
       <c r="G122" s="46"/>
@@ -5571,7 +5566,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="123" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E123" s="30"/>
       <c r="F123" s="30"/>
       <c r="G123" s="46"/>
@@ -5579,11 +5574,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="124" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E124" s="30"/>
       <c r="F124" s="46"/>
     </row>
-    <row r="125" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E125" s="30"/>
       <c r="F125" s="46"/>
       <c r="G125" s="30" t="str">
@@ -5594,7 +5589,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E126" s="30"/>
       <c r="F126" s="46"/>
       <c r="G126" s="30"/>
@@ -5633,7 +5628,7 @@
       <c r="AH126" s="28"/>
       <c r="AI126" s="29"/>
     </row>
-    <row r="127" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E127" s="30"/>
       <c r="F127" s="46"/>
       <c r="G127" s="30"/>
@@ -5672,7 +5667,7 @@
       <c r="AH127" s="19"/>
       <c r="AI127" s="20"/>
     </row>
-    <row r="128" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E128" s="30"/>
       <c r="F128" s="46"/>
       <c r="G128" s="30"/>
@@ -5711,7 +5706,7 @@
       <c r="AH128" s="43"/>
       <c r="AI128" s="44"/>
     </row>
-    <row r="129" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E129" s="30"/>
       <c r="F129" s="46"/>
       <c r="G129" s="30"/>
@@ -5750,7 +5745,7 @@
       <c r="AH129" s="19"/>
       <c r="AI129" s="20"/>
     </row>
-    <row r="130" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E130" s="30"/>
       <c r="F130" s="46"/>
       <c r="G130" s="30"/>
@@ -5785,7 +5780,7 @@
       <c r="AH130" s="19"/>
       <c r="AI130" s="20"/>
     </row>
-    <row r="131" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E131" s="30"/>
       <c r="F131" s="46"/>
       <c r="G131" s="30"/>
@@ -5820,7 +5815,7 @@
       <c r="AH131" s="41"/>
       <c r="AI131" s="42"/>
     </row>
-    <row r="132" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E132" s="30"/>
       <c r="F132" s="46"/>
       <c r="G132" s="30"/>
@@ -5859,7 +5854,7 @@
       <c r="AH132" s="41"/>
       <c r="AI132" s="42"/>
     </row>
-    <row r="133" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E133" s="30"/>
       <c r="F133" s="46"/>
       <c r="G133" s="30"/>
@@ -5898,7 +5893,7 @@
       <c r="AH133" s="19"/>
       <c r="AI133" s="20"/>
     </row>
-    <row r="134" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E134" s="30"/>
       <c r="F134" s="46"/>
       <c r="G134" s="30"/>
@@ -5933,7 +5928,7 @@
       <c r="AH134" s="19"/>
       <c r="AI134" s="20"/>
     </row>
-    <row r="135" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E135" s="30"/>
       <c r="F135" s="46"/>
       <c r="G135" s="30"/>
@@ -5970,7 +5965,7 @@
       <c r="AH135" s="19"/>
       <c r="AI135" s="20"/>
     </row>
-    <row r="136" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E136" s="30"/>
       <c r="F136" s="46"/>
       <c r="G136" s="30"/>
@@ -6007,7 +6002,7 @@
       <c r="AH136" s="19"/>
       <c r="AI136" s="20"/>
     </row>
-    <row r="137" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E137" s="30"/>
       <c r="F137" s="46"/>
       <c r="H137" s="18"/>
@@ -6043,7 +6038,7 @@
       <c r="AH137" s="19"/>
       <c r="AI137" s="20"/>
     </row>
-    <row r="138" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E138" s="30"/>
       <c r="F138" s="46"/>
       <c r="H138" s="40"/>
@@ -6075,7 +6070,7 @@
       <c r="AH138" s="41"/>
       <c r="AI138" s="42"/>
     </row>
-    <row r="139" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E139" s="30"/>
       <c r="F139" s="46"/>
       <c r="H139" s="40" t="s">
@@ -6113,7 +6108,7 @@
       <c r="AH139" s="41"/>
       <c r="AI139" s="42"/>
     </row>
-    <row r="140" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E140" s="30"/>
       <c r="F140" s="31"/>
       <c r="H140" s="40" t="s">
@@ -6151,7 +6146,7 @@
       <c r="AH140" s="41"/>
       <c r="AI140" s="42"/>
     </row>
-    <row r="141" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E141" s="30"/>
       <c r="H141" s="23" t="s">
         <v>134</v>
@@ -6188,7 +6183,7 @@
       <c r="AH141" s="24"/>
       <c r="AI141" s="25"/>
     </row>
-    <row r="142" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E142" s="30"/>
       <c r="H142" s="40"/>
       <c r="I142" s="41"/>
@@ -6222,8 +6217,8 @@
       <c r="AH142" s="41"/>
       <c r="AI142" s="42"/>
     </row>
-    <row r="143" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E144" s="30"/>
       <c r="F144" s="46" t="s">
         <v>15</v>
@@ -6232,7 +6227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E145" s="30"/>
       <c r="F145" s="46"/>
       <c r="G145" s="47" t="s">
@@ -6267,7 +6262,7 @@
       <c r="AH145" s="24"/>
       <c r="AI145" s="25"/>
     </row>
-    <row r="146" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E146" s="30"/>
       <c r="F146" s="46"/>
       <c r="G146" s="48" t="s">
@@ -6302,7 +6297,7 @@
       <c r="AH146" s="19"/>
       <c r="AI146" s="20"/>
     </row>
-    <row r="147" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E147" s="30"/>
       <c r="F147" s="46"/>
       <c r="G147" s="48" t="s">
@@ -6337,7 +6332,7 @@
       <c r="AH147" s="19"/>
       <c r="AI147" s="20"/>
     </row>
-    <row r="148" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E148" s="30"/>
       <c r="F148" s="46"/>
       <c r="G148" s="48" t="s">
@@ -6372,7 +6367,7 @@
       <c r="AH148" s="19"/>
       <c r="AI148" s="20"/>
     </row>
-    <row r="149" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E149" s="30"/>
       <c r="F149" s="46"/>
       <c r="G149" s="49" t="s">
@@ -6407,7 +6402,7 @@
       <c r="AH149" s="41"/>
       <c r="AI149" s="42"/>
     </row>
-    <row r="150" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E150" s="30"/>
       <c r="F150" s="46"/>
       <c r="G150" s="50"/>
@@ -6440,7 +6435,7 @@
       <c r="AH150" s="19"/>
       <c r="AI150" s="19"/>
     </row>
-    <row r="151" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E151" s="30" t="str">
         <f>$D$111&amp;"2."</f>
         <v>7.13.3.2.</v>
@@ -6449,7 +6444,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="152" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E152" s="30"/>
       <c r="F152" s="46" t="s">
         <v>12</v>
@@ -6458,7 +6453,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="153" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E153" s="30"/>
       <c r="F153" s="31"/>
       <c r="G153" s="27" t="s">
@@ -6499,7 +6494,7 @@
       <c r="AH153" s="28"/>
       <c r="AI153" s="29"/>
     </row>
-    <row r="154" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E154" s="30"/>
       <c r="F154" s="31"/>
       <c r="G154" s="32" t="s">
@@ -6540,7 +6535,7 @@
       <c r="AH154" s="43"/>
       <c r="AI154" s="44"/>
     </row>
-    <row r="155" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E155" s="30"/>
       <c r="F155" s="31"/>
       <c r="G155" s="18" t="s">
@@ -6581,7 +6576,7 @@
       <c r="AH155" s="19"/>
       <c r="AI155" s="20"/>
     </row>
-    <row r="156" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E156" s="30"/>
       <c r="F156" s="31"/>
       <c r="G156" s="40"/>
@@ -6616,7 +6611,7 @@
       <c r="AH156" s="41"/>
       <c r="AI156" s="42"/>
     </row>
-    <row r="157" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E157" s="30"/>
       <c r="F157" s="31"/>
       <c r="G157" s="32" t="s">
@@ -6657,7 +6652,7 @@
       <c r="AH157" s="43"/>
       <c r="AI157" s="44"/>
     </row>
-    <row r="158" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E158" s="30"/>
       <c r="F158" s="31"/>
       <c r="G158" s="32" t="s">
@@ -6698,11 +6693,11 @@
       <c r="AH158" s="43"/>
       <c r="AI158" s="44"/>
     </row>
-    <row r="159" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E159" s="30"/>
       <c r="F159" s="31"/>
     </row>
-    <row r="160" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="5:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E160" s="30"/>
       <c r="F160" s="46" t="s">
         <v>56</v>
@@ -6711,7 +6706,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="161" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E161" s="30"/>
       <c r="F161" s="46"/>
       <c r="G161" s="30" t="str">
@@ -6722,7 +6717,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D162" s="19"/>
       <c r="E162" s="37"/>
       <c r="F162" s="37"/>
@@ -6758,7 +6753,7 @@
       <c r="AH162" s="24"/>
       <c r="AI162" s="25"/>
     </row>
-    <row r="163" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E163" s="30"/>
       <c r="F163" s="30"/>
       <c r="G163" s="46"/>
@@ -6793,7 +6788,7 @@
       <c r="AH163" s="41"/>
       <c r="AI163" s="42"/>
     </row>
-    <row r="164" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E164" s="30"/>
       <c r="F164" s="30"/>
       <c r="G164" s="46"/>
@@ -6801,7 +6796,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="165" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E165" s="30"/>
       <c r="F165" s="30"/>
       <c r="G165" s="46"/>
@@ -6809,11 +6804,11 @@
         <v>122</v>
       </c>
     </row>
-    <row r="166" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E166" s="30"/>
       <c r="F166" s="46"/>
     </row>
-    <row r="167" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E167" s="30"/>
       <c r="F167" s="46"/>
       <c r="G167" s="30" t="str">
@@ -6824,7 +6819,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="168" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E168" s="30"/>
       <c r="F168" s="46"/>
       <c r="G168" s="30"/>
@@ -6863,7 +6858,7 @@
       <c r="AH168" s="28"/>
       <c r="AI168" s="29"/>
     </row>
-    <row r="169" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E169" s="30"/>
       <c r="H169" s="32" t="s">
         <v>78</v>
@@ -6900,7 +6895,7 @@
       <c r="AH169" s="43"/>
       <c r="AI169" s="44"/>
     </row>
-    <row r="170" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E170" s="30"/>
       <c r="H170" s="18" t="s">
         <v>17</v>
@@ -6937,7 +6932,7 @@
       <c r="AH170" s="19"/>
       <c r="AI170" s="20"/>
     </row>
-    <row r="171" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E171" s="30"/>
       <c r="H171" s="40"/>
       <c r="I171" s="41"/>
@@ -6970,7 +6965,7 @@
       <c r="AH171" s="41"/>
       <c r="AI171" s="42"/>
     </row>
-    <row r="172" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E172" s="30"/>
       <c r="H172" s="40" t="s">
         <v>106</v>
@@ -7007,7 +7002,7 @@
       <c r="AH172" s="41"/>
       <c r="AI172" s="42"/>
     </row>
-    <row r="173" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E173" s="30"/>
       <c r="H173" s="40" t="s">
         <v>82</v>
@@ -7044,7 +7039,7 @@
       <c r="AH173" s="41"/>
       <c r="AI173" s="42"/>
     </row>
-    <row r="174" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E174" s="30"/>
       <c r="H174" s="32" t="s">
         <v>123</v>
@@ -7081,7 +7076,7 @@
       <c r="AH174" s="43"/>
       <c r="AI174" s="44"/>
     </row>
-    <row r="175" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E175" s="30"/>
       <c r="H175" s="40" t="s">
         <v>90</v>
@@ -7118,7 +7113,7 @@
       <c r="AH175" s="41"/>
       <c r="AI175" s="42"/>
     </row>
-    <row r="176" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="4:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E176" s="30"/>
       <c r="H176" s="40" t="s">
         <v>94</v>
@@ -7155,7 +7150,7 @@
       <c r="AH176" s="41"/>
       <c r="AI176" s="42"/>
     </row>
-    <row r="177" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E177" s="30"/>
       <c r="H177" s="40" t="s">
         <v>96</v>
@@ -7192,7 +7187,7 @@
       <c r="AH177" s="41"/>
       <c r="AI177" s="42"/>
     </row>
-    <row r="178" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E178" s="30"/>
       <c r="H178" s="23" t="s">
         <v>98</v>
@@ -7229,7 +7224,7 @@
       <c r="AH178" s="24"/>
       <c r="AI178" s="25"/>
     </row>
-    <row r="179" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E179" s="30"/>
       <c r="H179" s="40"/>
       <c r="I179" s="41"/>
@@ -7263,7 +7258,7 @@
       <c r="AH179" s="41"/>
       <c r="AI179" s="42"/>
     </row>
-    <row r="180" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E180" s="30"/>
       <c r="H180" s="23" t="s">
         <v>126</v>
@@ -7280,7 +7275,7 @@
       <c r="P180" s="24"/>
       <c r="Q180" s="25"/>
       <c r="R180" s="23" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="S180" s="24"/>
       <c r="T180" s="24"/>
@@ -7300,7 +7295,7 @@
       <c r="AH180" s="24"/>
       <c r="AI180" s="25"/>
     </row>
-    <row r="181" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E181" s="30"/>
       <c r="H181" s="40"/>
       <c r="I181" s="41"/>
@@ -7313,7 +7308,7 @@
       <c r="P181" s="41"/>
       <c r="Q181" s="42"/>
       <c r="R181" s="40" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="S181" s="41"/>
       <c r="T181" s="41"/>
@@ -7333,7 +7328,7 @@
       <c r="AH181" s="41"/>
       <c r="AI181" s="42"/>
     </row>
-    <row r="182" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E182" s="30"/>
       <c r="H182" s="18" t="s">
         <v>128</v>
@@ -7370,7 +7365,7 @@
       <c r="AH182" s="19"/>
       <c r="AI182" s="20"/>
     </row>
-    <row r="183" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E183" s="30"/>
       <c r="H183" s="40"/>
       <c r="I183" s="41"/>
@@ -7403,7 +7398,7 @@
       <c r="AH183" s="41"/>
       <c r="AI183" s="42"/>
     </row>
-    <row r="184" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E184" s="30"/>
       <c r="H184" s="19"/>
       <c r="I184" s="19"/>
@@ -7434,7 +7429,7 @@
       <c r="AH184" s="19"/>
       <c r="AI184" s="19"/>
     </row>
-    <row r="185" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E185" s="30"/>
       <c r="F185" s="46" t="s">
         <v>15</v>
@@ -7443,14 +7438,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="186" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E186" s="30"/>
       <c r="F186" s="46"/>
       <c r="G186" s="45" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="187" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E187" s="30"/>
       <c r="F187" s="46"/>
       <c r="G187" s="47" t="s">
@@ -7485,7 +7480,7 @@
       <c r="AH187" s="24"/>
       <c r="AI187" s="25"/>
     </row>
-    <row r="188" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E188" s="30"/>
       <c r="F188" s="46"/>
       <c r="G188" s="49" t="s">
@@ -7520,7 +7515,7 @@
       <c r="AH188" s="41"/>
       <c r="AI188" s="42"/>
     </row>
-    <row r="189" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E189" s="30"/>
       <c r="F189" s="46"/>
       <c r="G189" s="50"/>
@@ -7553,7 +7548,7 @@
       <c r="AH189" s="19"/>
       <c r="AI189" s="19"/>
     </row>
-    <row r="190" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E190" s="30"/>
       <c r="F190" s="46"/>
       <c r="G190" s="50"/>
@@ -7586,7 +7581,7 @@
       <c r="AH190" s="19"/>
       <c r="AI190" s="19"/>
     </row>
-    <row r="191" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="45"/>
       <c r="B191" s="45"/>
       <c r="D191" s="46" t="str">
@@ -7599,23 +7594,23 @@
       <c r="AF191" s="45"/>
       <c r="AG191" s="45"/>
     </row>
-    <row r="192" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D192" s="46"/>
       <c r="E192" s="31" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="193" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="193" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D193" s="46"/>
       <c r="E193" s="31" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="194" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D194" s="46"/>
       <c r="E194" s="31"/>
     </row>
-    <row r="195" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D195" s="46"/>
       <c r="E195" s="27" t="s">
         <v>10</v>
@@ -7650,7 +7645,7 @@
       <c r="AE195" s="28"/>
       <c r="AF195" s="29"/>
     </row>
-    <row r="196" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="196" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D196" s="46"/>
       <c r="E196" s="58" t="s">
         <v>37</v>
@@ -7660,7 +7655,7 @@
       <c r="H196" s="24"/>
       <c r="I196" s="25"/>
       <c r="J196" s="59" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="K196" s="59"/>
       <c r="L196" s="59"/>
@@ -7685,7 +7680,7 @@
       <c r="AE196" s="59"/>
       <c r="AF196" s="60"/>
     </row>
-    <row r="197" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="197" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D197" s="46"/>
       <c r="E197" s="57"/>
       <c r="F197" s="41"/>
@@ -7716,7 +7711,7 @@
       <c r="AE197" s="61"/>
       <c r="AF197" s="62"/>
     </row>
-    <row r="198" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="198" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D198" s="46"/>
       <c r="E198" s="58" t="s">
         <v>39</v>
@@ -7726,7 +7721,7 @@
       <c r="H198" s="24"/>
       <c r="I198" s="25"/>
       <c r="J198" s="59" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="K198" s="59"/>
       <c r="L198" s="59"/>
@@ -7751,7 +7746,7 @@
       <c r="AE198" s="59"/>
       <c r="AF198" s="60"/>
     </row>
-    <row r="199" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="199" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D199" s="46"/>
       <c r="E199" s="57"/>
       <c r="F199" s="41"/>
@@ -7782,7 +7777,7 @@
       <c r="AE199" s="61"/>
       <c r="AF199" s="62"/>
     </row>
-    <row r="200" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="200" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D200" s="46"/>
       <c r="E200" s="58" t="s">
         <v>41</v>
@@ -7792,7 +7787,7 @@
       <c r="H200" s="24"/>
       <c r="I200" s="25"/>
       <c r="J200" s="59" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="K200" s="59"/>
       <c r="L200" s="59"/>
@@ -7817,7 +7812,7 @@
       <c r="AE200" s="59"/>
       <c r="AF200" s="60"/>
     </row>
-    <row r="201" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="201" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D201" s="46"/>
       <c r="E201" s="57"/>
       <c r="F201" s="41"/>
@@ -7848,7 +7843,7 @@
       <c r="AE201" s="61"/>
       <c r="AF201" s="62"/>
     </row>
-    <row r="202" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="202" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D202" s="46"/>
       <c r="E202" s="58" t="s">
         <v>44</v>
@@ -7858,7 +7853,7 @@
       <c r="H202" s="24"/>
       <c r="I202" s="25"/>
       <c r="J202" s="63" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="K202" s="59"/>
       <c r="L202" s="59"/>
@@ -7883,7 +7878,7 @@
       <c r="AE202" s="59"/>
       <c r="AF202" s="60"/>
     </row>
-    <row r="203" spans="4:32" s="45" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="203" spans="4:32" s="45" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D203" s="46"/>
       <c r="E203" s="57"/>
       <c r="F203" s="41"/>
@@ -7914,46 +7909,46 @@
       <c r="AE203" s="61"/>
       <c r="AF203" s="62"/>
     </row>
-    <row r="204" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E205" s="45" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="206" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="206" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E207" s="31" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="208" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="208" spans="4:32" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E208" s="31" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="209" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="209" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E210" s="46" t="str">
         <f>$D$191&amp;"1."</f>
         <v>7.13.4.1.</v>
       </c>
       <c r="F210" s="45" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="211" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="211" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E211" s="46"/>
       <c r="F211" s="30" t="str">
         <f>$E$210&amp;"1."</f>
         <v>7.13.4.1.1.</v>
       </c>
       <c r="G211" s="45" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="212" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="212" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G212" s="23" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H212" s="24"/>
       <c r="I212" s="24"/>
@@ -7983,15 +7978,15 @@
       <c r="AG212" s="24"/>
       <c r="AH212" s="25"/>
     </row>
-    <row r="213" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G213" s="18" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AH213" s="20"/>
     </row>
-    <row r="214" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G214" s="40" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H214" s="41"/>
       <c r="I214" s="41"/>
@@ -8021,48 +8016,48 @@
       <c r="AG214" s="41"/>
       <c r="AH214" s="42"/>
     </row>
-    <row r="215" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="215" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G215" s="36" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="216" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="216" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G216" s="45" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="217" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="217" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G217" s="36" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="218" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="218" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D218" s="46"/>
       <c r="E218" s="31"/>
     </row>
-    <row r="219" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="219" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E219" s="46" t="str">
         <f>$D$191&amp;"2."</f>
         <v>7.13.4.2.</v>
       </c>
       <c r="F219" s="45" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="220" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="220" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E220" s="46"/>
       <c r="F220" s="30" t="str">
         <f>$E$219&amp;"1."</f>
         <v>7.13.4.2.1.</v>
       </c>
       <c r="G220" s="45" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="221" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="221" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E221" s="30"/>
       <c r="G221" s="39" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H221" s="24"/>
       <c r="I221" s="24"/>
@@ -8092,45 +8087,45 @@
       <c r="AG221" s="24"/>
       <c r="AH221" s="25"/>
     </row>
-    <row r="222" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E222" s="30"/>
       <c r="G222" s="18" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AH222" s="20"/>
     </row>
-    <row r="223" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E223" s="30"/>
       <c r="G223" s="18" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AH223" s="20"/>
     </row>
-    <row r="224" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="4:34" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E224" s="30"/>
       <c r="G224" s="18" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AH224" s="20"/>
     </row>
-    <row r="225" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E225" s="30"/>
       <c r="G225" s="18" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AH225" s="20"/>
     </row>
-    <row r="226" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E226" s="30"/>
       <c r="G226" s="18" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AH226" s="20"/>
     </row>
-    <row r="227" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E227" s="30"/>
       <c r="G227" s="40" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H227" s="41"/>
       <c r="I227" s="41"/>
@@ -8160,18 +8155,18 @@
       <c r="AG227" s="41"/>
       <c r="AH227" s="42"/>
     </row>
-    <row r="228" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G228" s="36" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="229" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G229" s="45" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="230" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="230" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" spans="1:35" s="45" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E231" s="30"/>
       <c r="F231" s="46"/>
       <c r="G231" s="50"/>
@@ -8204,7 +8199,7 @@
       <c r="AH231" s="19"/>
       <c r="AI231" s="19"/>
     </row>
-    <row r="232" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="45"/>
       <c r="B232" s="45"/>
       <c r="D232" s="46" t="str">
@@ -8218,7 +8213,7 @@
       <c r="AF232" s="45"/>
       <c r="AG232" s="45"/>
     </row>
-    <row r="233" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="45"/>
       <c r="B233" s="45"/>
       <c r="E233" s="31" t="s">
@@ -8228,50 +8223,50 @@
       <c r="AF233" s="45"/>
       <c r="AG233" s="45"/>
     </row>
-    <row r="234" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:35" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="45"/>
       <c r="B234" s="45"/>
       <c r="E234" s="30"/>
       <c r="AF234" s="45"/>
       <c r="AG234" s="45"/>
     </row>
-    <row r="235" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AF235" s="45"/>
       <c r="AG235" s="45"/>
     </row>
-    <row r="236" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="46" t="str">
         <f>$C$7&amp;"6."</f>
         <v>7.13.6.</v>
       </c>
       <c r="E236" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="237" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E237" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="238" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E238" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="240" spans="1:35" s="45" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E240" s="45" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="237" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E237" s="4" t="s">
+    <row r="241" spans="5:5" s="45" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" spans="5:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E242" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="244" spans="5:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E244" s="4" t="s">
         <v>264</v>
-      </c>
-    </row>
-    <row r="238" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E238" s="4" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="240" spans="1:35" s="45" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E240" s="45" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="241" spans="5:5" s="45" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" spans="5:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E242" s="4" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="244" spans="5:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E244" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>
